--- a/AAII_Financials/Quarterly/PAX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PAX_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="92">
   <si>
     <t>PAX</t>
   </si>
@@ -656,88 +656,88 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43830</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43738</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
@@ -747,59 +747,62 @@
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>111700</v>
+      </c>
+      <c r="E8" s="3">
         <v>63500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>78600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>73800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>91300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>57000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>55600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>55000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>46200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>39700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>119000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>30600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>31800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>83300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>35200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>88000</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
@@ -809,59 +812,62 @@
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>50100</v>
+      </c>
+      <c r="E9" s="3">
         <v>27900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>35900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>34800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>40800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>26000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>27400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>27600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>16400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>15200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>43100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>12000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>7200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>26000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>8700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>34200</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
@@ -871,59 +877,62 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>61600</v>
+      </c>
+      <c r="E10" s="3">
         <v>35600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>42700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>39000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>50500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>31000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>28200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>27400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>29800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>24500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>75900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>18600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>24600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>57300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>26500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>53800</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
@@ -933,8 +942,11 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -957,8 +969,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1019,8 +1032,11 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1081,8 +1097,11 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1101,30 +1120,30 @@
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>5100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>8900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>100</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>2400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>2200</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1134,8 +1153,8 @@
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1143,8 +1162,11 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1163,14 +1185,14 @@
       <c r="H15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I15" s="3">
+      <c r="I15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J15" s="3">
         <v>1800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1600</v>
-      </c>
-      <c r="K15" s="3">
-        <v>500</v>
       </c>
       <c r="L15" s="3">
         <v>500</v>
@@ -1182,20 +1204,20 @@
         <v>500</v>
       </c>
       <c r="O15" s="3">
+        <v>500</v>
+      </c>
+      <c r="P15" s="3">
         <v>400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>1700</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1205,8 +1227,11 @@
       <c r="V15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1226,59 +1251,60 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>57900</v>
+      </c>
+      <c r="E17" s="3">
         <v>46200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>51000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>52100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>44400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>40900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>42100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>37100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>31700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>18300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>46900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>16800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>15100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>34700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>14600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>44000</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1288,59 +1314,62 @@
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>53800</v>
+      </c>
+      <c r="E18" s="3">
         <v>17300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>27600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>21700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>46900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>16100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>13500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>17900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>14500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>21400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>72100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>13800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>16700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>48600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>20600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>44000</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1350,8 +1379,11 @@
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1374,59 +1406,60 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E20" s="3">
         <v>1000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>5200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>400</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>600</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>900</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1436,8 +1469,11 @@
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1456,39 +1492,39 @@
       <c r="H21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I21" s="3">
+      <c r="I21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J21" s="3">
         <v>21300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>28300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>24100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>22900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>76400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>15800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>18600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>55000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>22700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>51100</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1498,8 +1534,11 @@
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1518,14 +1557,14 @@
       <c r="H22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I22" s="3">
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3">
         <v>700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>600</v>
-      </c>
-      <c r="K22" s="3">
-        <v>300</v>
       </c>
       <c r="L22" s="3">
         <v>300</v>
@@ -1537,20 +1576,20 @@
         <v>300</v>
       </c>
       <c r="O22" s="3">
+        <v>300</v>
+      </c>
+      <c r="P22" s="3">
         <v>200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>800</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1560,59 +1599,62 @@
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>50400</v>
+      </c>
+      <c r="E23" s="3">
         <v>18300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>28400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>23000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>49000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>15400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>15600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>22500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>15100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>20700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>72200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>13600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>16500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>48500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>20300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>44100</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1622,59 +1664,62 @@
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E24" s="3">
         <v>-600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-7700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3100</v>
-      </c>
-      <c r="G24" s="3">
-        <v>2200</v>
       </c>
       <c r="H24" s="3">
         <v>2200</v>
       </c>
       <c r="I24" s="3">
+        <v>2200</v>
+      </c>
+      <c r="J24" s="3">
         <v>-300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-1200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>3000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2700</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1684,8 +1729,11 @@
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1746,59 +1794,62 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>48100</v>
+      </c>
+      <c r="E26" s="3">
         <v>18900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>36100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>19900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>46700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>13200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>15900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>18300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>13200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>21500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>73400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>13100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>16300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>45500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>19600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>41400</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1808,59 +1859,62 @@
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>47000</v>
+      </c>
+      <c r="E27" s="3">
         <v>18500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>35700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>19400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>46600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>12200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>15900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>18300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>13200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>21500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>73400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>14300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>15600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>46600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>18700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>39800</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1870,8 +1924,11 @@
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1932,8 +1989,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1994,8 +2054,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2056,8 +2119,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2118,59 +2184,62 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-5200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-400</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-600</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-900</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2180,59 +2249,62 @@
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>47000</v>
+      </c>
+      <c r="E33" s="3">
         <v>18500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>35700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>19400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>46600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>12200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>15900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>18300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>13200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>21500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>73400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>14300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>15600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>46600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>18700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>39800</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2242,8 +2314,11 @@
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2304,59 +2379,62 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>47000</v>
+      </c>
+      <c r="E35" s="3">
         <v>18500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>35700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>19400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>46600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>12200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>15900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>18300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>13200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>21500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>73400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>14300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>15600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>46600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>18700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>39800</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2366,64 +2444,67 @@
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43830</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43738</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2433,8 +2514,11 @@
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2457,8 +2541,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2481,53 +2566,54 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E41" s="3">
         <v>17500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>22400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>30800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>21400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>24400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>13400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>12900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>15300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>44300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>25200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>28700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>14100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>39700</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2543,53 +2629,56 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>204500</v>
+      </c>
+      <c r="E42" s="3">
         <v>205500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>205600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>253400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>291000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>317000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>328400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>136000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>151900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>250800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>286300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>300400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>9900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>11600</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2605,53 +2694,56 @@
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>149000</v>
+      </c>
+      <c r="E43" s="3">
         <v>135400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>120600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>151900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>137900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>95900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>95600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>105400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>103500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>122300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>113700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>24400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>26000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>10000</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2667,8 +2759,11 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2729,53 +2824,56 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>29100</v>
+      </c>
+      <c r="E45" s="3">
         <v>21000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>29200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>28100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>29300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>51600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>55500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>83900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>81700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1800</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2791,53 +2889,56 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>398700</v>
+      </c>
+      <c r="E46" s="3">
         <v>379400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>377800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>464200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>479600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>488900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>492900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>338200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>352300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>421400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>428200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>355500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>53700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>63100</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2853,53 +2954,56 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>75500</v>
+      </c>
+      <c r="E47" s="3">
         <v>73000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>75700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>70000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>50400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>58600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>44100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>282900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>30000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>30600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>31100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>30400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>24500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>36500</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2915,53 +3019,56 @@
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>28200</v>
+      </c>
+      <c r="E48" s="3">
         <v>23800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>25400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>25200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>24600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>24000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>18300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>15800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>13400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3900</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2977,53 +3084,56 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>500400</v>
+      </c>
+      <c r="E49" s="3">
         <v>438400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>452400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>417900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>411500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>359500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>339800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>366300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>358900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>18300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>19300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>21400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>22400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>23700</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3039,8 +3149,11 @@
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3101,8 +3214,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3163,8 +3279,11 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3172,44 +3291,44 @@
         <v>22200</v>
       </c>
       <c r="E52" s="3">
+        <v>22200</v>
+      </c>
+      <c r="F52" s="3">
         <v>19500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>21700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>10000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5700</v>
-      </c>
-      <c r="I52" s="3">
-        <v>5500</v>
       </c>
       <c r="J52" s="3">
         <v>5500</v>
       </c>
       <c r="K52" s="3">
+        <v>5500</v>
+      </c>
+      <c r="L52" s="3">
         <v>6700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2800</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3225,8 +3344,11 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3287,53 +3409,56 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1025000</v>
+      </c>
+      <c r="E54" s="3">
         <v>936800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>950800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>999000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>976200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>936700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>900700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1008700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>761300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>478500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>486400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>413500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>107200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>130000</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3349,8 +3474,11 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3373,8 +3501,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3397,8 +3526,9 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3459,8 +3589,11 @@
       <c r="V57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3473,39 +3606,39 @@
       <c r="F58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G58" s="3">
+      <c r="G58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H58" s="3">
         <v>2200</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I58" s="3">
+      <c r="I58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J58" s="3">
         <v>1200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>700</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3521,53 +3654,56 @@
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>397500</v>
+      </c>
+      <c r="E59" s="3">
         <v>323000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>280700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>371200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>335800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>347600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>312600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>164600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>155300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>84700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>51400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>38600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>43300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>33900</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3583,53 +3719,56 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>397500</v>
+      </c>
+      <c r="E60" s="3">
         <v>323000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>280700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>371200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>338000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>347600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>313900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>166200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>156200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>85600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>52400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>39500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>44000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>34600</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3645,8 +3784,11 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3660,38 +3802,38 @@
         <v>0</v>
       </c>
       <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
         <v>13900</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>8800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>7300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>900</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3707,53 +3849,56 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>92800</v>
+      </c>
+      <c r="E62" s="3">
         <v>140300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>161300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>131800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>110900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>73500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>44500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>261900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>33900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3900</v>
-      </c>
-      <c r="M62" s="3">
-        <v>2900</v>
       </c>
       <c r="N62" s="3">
         <v>2900</v>
       </c>
       <c r="O62" s="3">
+        <v>2900</v>
+      </c>
+      <c r="P62" s="3">
         <v>3300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4400</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3769,8 +3914,11 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3831,8 +3979,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3893,8 +4044,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3955,53 +4109,56 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>482800</v>
+      </c>
+      <c r="E66" s="3">
         <v>422500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>410100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>460900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>423500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>422300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>367200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>435300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>197000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>90300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>56300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>43200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>49900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>40100</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4017,8 +4174,11 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4041,8 +4201,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4103,8 +4264,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4165,8 +4329,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4227,8 +4394,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4289,53 +4459,56 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>50800</v>
+      </c>
+      <c r="E72" s="3">
         <v>33300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>51900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>51600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>79100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>56200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>70000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>83700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>88700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>94500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>135900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>76300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>62000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>96200</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4351,8 +4524,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4413,8 +4589,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4475,8 +4654,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4537,53 +4719,56 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>542200</v>
+      </c>
+      <c r="E76" s="3">
         <v>514300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>540700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>538100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>552800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>514400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>533500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>573400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>564300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>388200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>430100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>370300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>57300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>89900</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4599,8 +4784,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4661,64 +4849,67 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43830</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43738</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4728,59 +4919,62 @@
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>47000</v>
+      </c>
+      <c r="E81" s="3">
         <v>18500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>35700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>19400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>46600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>12200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>15900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>18300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>13200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>21500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>73400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>14300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>15600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>46600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>18700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>39800</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4790,8 +4984,11 @@
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4814,8 +5011,9 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4834,39 +5032,39 @@
       <c r="H83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I83" s="3">
+      <c r="I83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J83" s="3">
         <v>5100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>5200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>8800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>5800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>6200</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4876,8 +5074,11 @@
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4938,8 +5139,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5000,8 +5204,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5062,8 +5269,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5124,8 +5334,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5186,8 +5399,11 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -5206,39 +5422,39 @@
       <c r="H89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I89" s="3">
+      <c r="I89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J89" s="3">
         <v>7700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>26300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>107600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>47800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>31700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>34600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-6600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>59300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-4200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>48600</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5248,8 +5464,11 @@
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5272,59 +5491,60 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1400</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-800</v>
       </c>
       <c r="H91" s="3">
         <v>-800</v>
       </c>
       <c r="I91" s="3">
-        <v>0</v>
+        <v>-800</v>
       </c>
       <c r="J91" s="3">
         <v>0</v>
       </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-200</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-200</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5334,8 +5554,11 @@
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5396,8 +5619,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5458,8 +5684,11 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5478,39 +5707,39 @@
       <c r="H94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I94" s="3">
+      <c r="I94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J94" s="3">
         <v>27900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-230900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-284200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>34800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-283200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-297400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>6500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>17000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-21000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>32300</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5520,8 +5749,11 @@
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5544,8 +5776,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5565,26 +5798,26 @@
         <v>0</v>
       </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>-29700</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-23600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-119800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-63000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-37700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-23300</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
@@ -5606,8 +5839,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5668,8 +5904,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5730,8 +5969,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5792,8 +6034,11 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -5812,39 +6057,39 @@
       <c r="H100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I100" s="3">
+      <c r="I100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J100" s="3">
         <v>-30500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>201100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>177900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-63500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>262400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>277300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-25600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-40600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-53300</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5854,8 +6099,11 @@
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5874,29 +6122,29 @@
       <c r="H101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I101" s="3">
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3">
         <v>-1500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1200</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
       <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
         <v>-100</v>
-      </c>
-      <c r="M101" s="3">
-        <v>200</v>
       </c>
       <c r="N101" s="3">
         <v>200</v>
       </c>
       <c r="O101" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="P101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Q101" s="3">
         <v>-100</v>
@@ -5904,8 +6152,8 @@
       <c r="R101" s="3">
         <v>-100</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>3</v>
+      <c r="S101" s="3">
+        <v>-100</v>
       </c>
       <c r="T101" s="3" t="s">
         <v>3</v>
@@ -5916,8 +6164,11 @@
       <c r="V101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -5936,39 +6187,39 @@
       <c r="H102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I102" s="3">
+      <c r="I102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J102" s="3">
         <v>3500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>19100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>11100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>14700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-25600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>35600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-25800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>27600</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5976,6 +6227,9 @@
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PAX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PAX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="92">
   <si>
     <t>PAX</t>
   </si>
@@ -656,91 +656,92 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
@@ -750,62 +751,65 @@
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>111700</v>
+        <v>63900</v>
       </c>
       <c r="E8" s="3">
-        <v>63500</v>
+        <v>111900</v>
       </c>
       <c r="F8" s="3">
+        <v>64500</v>
+      </c>
+      <c r="G8" s="3">
         <v>78600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>73800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>91300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>57000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>55600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>55000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>46200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>39700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>119000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>30600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>31800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>83300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>35200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>88000</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
@@ -815,62 +819,65 @@
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>26900</v>
+      </c>
+      <c r="E9" s="3">
         <v>50100</v>
       </c>
-      <c r="E9" s="3">
-        <v>27900</v>
-      </c>
       <c r="F9" s="3">
+        <v>28000</v>
+      </c>
+      <c r="G9" s="3">
         <v>35900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>34800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>40800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>26000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>27400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>27600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>16400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>15200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>43100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>12000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>7200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>26000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>8700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>34200</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
@@ -880,62 +887,65 @@
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>61600</v>
+        <v>37000</v>
       </c>
       <c r="E10" s="3">
-        <v>35600</v>
+        <v>61800</v>
       </c>
       <c r="F10" s="3">
+        <v>36500</v>
+      </c>
+      <c r="G10" s="3">
         <v>42700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>39000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>50500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>31000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>28200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>27400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>29800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>24500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>75900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>18600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>24600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>57300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>26500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>53800</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
@@ -945,8 +955,11 @@
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -970,8 +983,9 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1035,8 +1049,11 @@
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1100,19 +1117,22 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
+      <c r="E14" s="3">
+        <v>6100</v>
+      </c>
+      <c r="F14" s="3">
+        <v>2600</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
@@ -1123,30 +1143,30 @@
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>5100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>8900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>100</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>2400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>2200</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1156,8 +1176,8 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1165,19 +1185,22 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>3</v>
+      <c r="E15" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F15" s="3">
+        <v>1300</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>3</v>
@@ -1188,14 +1211,14 @@
       <c r="I15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J15" s="3">
+      <c r="J15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K15" s="3">
         <v>1800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1600</v>
-      </c>
-      <c r="L15" s="3">
-        <v>500</v>
       </c>
       <c r="M15" s="3">
         <v>500</v>
@@ -1207,20 +1230,20 @@
         <v>500</v>
       </c>
       <c r="P15" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q15" s="3">
         <v>400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>1300</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>1700</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1230,8 +1253,11 @@
       <c r="W15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1252,62 +1278,63 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>57900</v>
+        <v>43100</v>
       </c>
       <c r="E17" s="3">
-        <v>46200</v>
+        <v>53300</v>
       </c>
       <c r="F17" s="3">
+        <v>45000</v>
+      </c>
+      <c r="G17" s="3">
         <v>51000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>52100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>44400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>40900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>42100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>37100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>31700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>18300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>46900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>16800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>15100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>34700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>14600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>44000</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1317,62 +1344,65 @@
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>53800</v>
+        <v>20800</v>
       </c>
       <c r="E18" s="3">
-        <v>17300</v>
+        <v>58600</v>
       </c>
       <c r="F18" s="3">
+        <v>19500</v>
+      </c>
+      <c r="G18" s="3">
         <v>27600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>21700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>46900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>16100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>13500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>17900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>14500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>21400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>72100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>13800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>16700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>48600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>20600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>44000</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1382,8 +1412,11 @@
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1407,62 +1440,63 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-3400</v>
+        <v>-800</v>
       </c>
       <c r="E20" s="3">
-        <v>1000</v>
+        <v>-7700</v>
       </c>
       <c r="F20" s="3">
+        <v>-900</v>
+      </c>
+      <c r="G20" s="3">
         <v>800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>5200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>400</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>600</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>900</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1472,8 +1506,11 @@
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1495,39 +1532,39 @@
       <c r="I21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J21" s="3">
+      <c r="J21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K21" s="3">
         <v>21300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>28300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>24100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>22900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>76400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>15800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>18600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>55000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>22700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>51100</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1537,19 +1574,22 @@
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>3</v>
+      <c r="E22" s="3">
+        <v>300</v>
+      </c>
+      <c r="F22" s="3">
+        <v>300</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>3</v>
@@ -1560,14 +1600,14 @@
       <c r="I22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J22" s="3">
+      <c r="J22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K22" s="3">
         <v>700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>600</v>
-      </c>
-      <c r="L22" s="3">
-        <v>300</v>
       </c>
       <c r="M22" s="3">
         <v>300</v>
@@ -1579,20 +1619,20 @@
         <v>300</v>
       </c>
       <c r="P22" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q22" s="3">
         <v>200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>800</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1602,62 +1642,65 @@
       <c r="W22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>50400</v>
+        <v>20000</v>
       </c>
       <c r="E23" s="3">
+        <v>50700</v>
+      </c>
+      <c r="F23" s="3">
         <v>18300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>28400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>23000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>49000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>15400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>15600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>22500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>15100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>20700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>72200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>13600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>16500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>48500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>20300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>44100</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1667,62 +1710,65 @@
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E24" s="3">
         <v>2300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-7700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3100</v>
-      </c>
-      <c r="H24" s="3">
-        <v>2200</v>
       </c>
       <c r="I24" s="3">
         <v>2200</v>
       </c>
       <c r="J24" s="3">
+        <v>2200</v>
+      </c>
+      <c r="K24" s="3">
         <v>-300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>4200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-1200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>3000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2700</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1732,8 +1778,11 @@
       <c r="W24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1797,62 +1846,65 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>48100</v>
+        <v>15800</v>
       </c>
       <c r="E26" s="3">
-        <v>18900</v>
+        <v>48400</v>
       </c>
       <c r="F26" s="3">
+        <v>18800</v>
+      </c>
+      <c r="G26" s="3">
         <v>36100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>19900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>46700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>13200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>15900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>18300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>13200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>21500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>73400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>13100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>16300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>45500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>19600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>41400</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1862,62 +1914,65 @@
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>15400</v>
+      </c>
+      <c r="E27" s="3">
         <v>47000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>18500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>35700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>19400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>46600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>12200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>15900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>18300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>13200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>21500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>73400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>14300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>15600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>46600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>18700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>39800</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1927,8 +1982,11 @@
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1992,8 +2050,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2057,8 +2118,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2122,8 +2186,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2187,62 +2254,65 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>3400</v>
+        <v>800</v>
       </c>
       <c r="E32" s="3">
-        <v>-1000</v>
+        <v>7700</v>
       </c>
       <c r="F32" s="3">
+        <v>900</v>
+      </c>
+      <c r="G32" s="3">
         <v>-800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-5200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-400</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-600</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-900</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2252,62 +2322,65 @@
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>15400</v>
+      </c>
+      <c r="E33" s="3">
         <v>47000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>18500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>35700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>19400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>46600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>12200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>15900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>18300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>13200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>21500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>73400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>14300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>15600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>46600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>18700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>39800</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2317,8 +2390,11 @@
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2382,62 +2458,65 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>15400</v>
+      </c>
+      <c r="E35" s="3">
         <v>47000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>18500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>35700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>19400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>46600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>12200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>15900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>18300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>13200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>21500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>73400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>14300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>15600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>46600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>18700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>39800</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2447,67 +2526,70 @@
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2517,8 +2599,11 @@
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2542,8 +2627,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2567,56 +2653,57 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>16100</v>
+        <v>17300</v>
       </c>
       <c r="E41" s="3">
-        <v>17500</v>
+        <v>12000</v>
       </c>
       <c r="F41" s="3">
+        <v>12800</v>
+      </c>
+      <c r="G41" s="3">
         <v>22400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>30800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>21400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>24400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>13400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>12900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>15300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>44300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>25200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>28700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>14100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>39700</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2632,56 +2719,59 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>204500</v>
+        <v>197600</v>
       </c>
       <c r="E42" s="3">
-        <v>205500</v>
+        <v>208500</v>
       </c>
       <c r="F42" s="3">
+        <v>210200</v>
+      </c>
+      <c r="G42" s="3">
         <v>205600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>253400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>291000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>317000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>328400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>136000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>151900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>250800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>286300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>300400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>9900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>11600</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2697,56 +2787,59 @@
       <c r="W42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>149000</v>
+        <v>142400</v>
       </c>
       <c r="E43" s="3">
-        <v>135400</v>
+        <v>152200</v>
       </c>
       <c r="F43" s="3">
+        <v>130100</v>
+      </c>
+      <c r="G43" s="3">
         <v>120600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>151900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>137900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>95900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>95600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>105400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>103500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>122300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>113700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>24400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>26000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>10000</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2762,8 +2855,11 @@
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2827,56 +2923,59 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>29100</v>
+        <v>89500</v>
       </c>
       <c r="E45" s="3">
-        <v>21000</v>
+        <v>28800</v>
       </c>
       <c r="F45" s="3">
+        <v>19200</v>
+      </c>
+      <c r="G45" s="3">
         <v>29200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>28100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>29300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>51600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>55500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>83900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>81700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1800</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2892,56 +2991,59 @@
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>398700</v>
+        <v>446800</v>
       </c>
       <c r="E46" s="3">
-        <v>379400</v>
+        <v>401600</v>
       </c>
       <c r="F46" s="3">
+        <v>372400</v>
+      </c>
+      <c r="G46" s="3">
         <v>377800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>464200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>479600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>488900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>492900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>338200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>352300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>421400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>428200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>355500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>53700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>63100</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2957,56 +3059,59 @@
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>74200</v>
+      </c>
+      <c r="E47" s="3">
         <v>75500</v>
       </c>
-      <c r="E47" s="3">
-        <v>73000</v>
-      </c>
       <c r="F47" s="3">
+        <v>72900</v>
+      </c>
+      <c r="G47" s="3">
         <v>75700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>70000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>50400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>58600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>44100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>282900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>30000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>30600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>31100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>30400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>24500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>36500</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3022,56 +3127,59 @@
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>28800</v>
+      </c>
+      <c r="E48" s="3">
         <v>28200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>23800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>25400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>25200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>24600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>24000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>18300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>15800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>13400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3900</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3087,56 +3195,59 @@
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>500400</v>
+        <v>473500</v>
       </c>
       <c r="E49" s="3">
+        <v>487000</v>
+      </c>
+      <c r="F49" s="3">
         <v>438400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>452400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>417900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>411500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>359500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>339800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>366300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>358900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>18300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>19300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>21400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>22400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>23700</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3152,8 +3263,11 @@
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3217,8 +3331,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3282,56 +3399,59 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>22200</v>
+        <v>21100</v>
       </c>
       <c r="E52" s="3">
-        <v>22200</v>
+        <v>19300</v>
       </c>
       <c r="F52" s="3">
+        <v>22100</v>
+      </c>
+      <c r="G52" s="3">
         <v>19500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>21700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>10000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5700</v>
-      </c>
-      <c r="J52" s="3">
-        <v>5500</v>
       </c>
       <c r="K52" s="3">
         <v>5500</v>
       </c>
       <c r="L52" s="3">
+        <v>5500</v>
+      </c>
+      <c r="M52" s="3">
         <v>6700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2800</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3347,8 +3467,11 @@
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3412,56 +3535,59 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1025000</v>
+        <v>1044400</v>
       </c>
       <c r="E54" s="3">
-        <v>936800</v>
+        <v>1011600</v>
       </c>
       <c r="F54" s="3">
+        <v>929600</v>
+      </c>
+      <c r="G54" s="3">
         <v>950800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>999000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>976200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>936700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>900700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1008700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>761300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>478500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>486400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>413500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>107200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>130000</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3477,8 +3603,11 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3502,8 +3631,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3527,8 +3657,9 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3592,56 +3723,59 @@
       <c r="W57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
+      <c r="D58" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F58" s="3">
+        <v>2900</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H58" s="3">
+      <c r="H58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I58" s="3">
         <v>2200</v>
       </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3">
+      <c r="J58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K58" s="3">
         <v>1200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>700</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3657,56 +3791,59 @@
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>397500</v>
+        <v>384400</v>
       </c>
       <c r="E59" s="3">
-        <v>323000</v>
+        <v>394500</v>
       </c>
       <c r="F59" s="3">
+        <v>313100</v>
+      </c>
+      <c r="G59" s="3">
         <v>280700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>371200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>335800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>347600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>312600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>164600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>155300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>84700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>51400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>38600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>43300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>33900</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3722,56 +3859,59 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>394400</v>
+      </c>
+      <c r="E60" s="3">
         <v>397500</v>
       </c>
-      <c r="E60" s="3">
-        <v>323000</v>
-      </c>
       <c r="F60" s="3">
+        <v>316000</v>
+      </c>
+      <c r="G60" s="3">
         <v>280700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>371200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>338000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>347600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>313900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>166200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>156200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>85600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>52400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>39500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>44000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>34600</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3787,56 +3927,59 @@
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>73400</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>12800</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>12700</v>
       </c>
       <c r="G61" s="3">
         <v>0</v>
       </c>
       <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>13900</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>8800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>900</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -3852,56 +3995,59 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>92800</v>
+        <v>88100</v>
       </c>
       <c r="E62" s="3">
-        <v>140300</v>
+        <v>79900</v>
       </c>
       <c r="F62" s="3">
+        <v>127500</v>
+      </c>
+      <c r="G62" s="3">
         <v>161300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>131800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>110900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>73500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>44500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>261900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>33900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3900</v>
-      </c>
-      <c r="N62" s="3">
-        <v>2900</v>
       </c>
       <c r="O62" s="3">
         <v>2900</v>
       </c>
       <c r="P62" s="3">
+        <v>2900</v>
+      </c>
+      <c r="Q62" s="3">
         <v>3300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4400</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3917,8 +4063,11 @@
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3982,8 +4131,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4047,8 +4199,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4112,56 +4267,59 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>482800</v>
+        <v>539300</v>
       </c>
       <c r="E66" s="3">
-        <v>422500</v>
+        <v>469100</v>
       </c>
       <c r="F66" s="3">
+        <v>415500</v>
+      </c>
+      <c r="G66" s="3">
         <v>410100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>460900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>423500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>422300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>367200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>435300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>197000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>90300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>56300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>43200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>49900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>40100</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4177,8 +4335,11 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4202,8 +4363,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4267,8 +4429,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4332,8 +4497,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4397,8 +4565,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4462,56 +4633,59 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>50800</v>
+        <v>8400</v>
       </c>
       <c r="E72" s="3">
-        <v>33300</v>
+        <v>53800</v>
       </c>
       <c r="F72" s="3">
+        <v>35700</v>
+      </c>
+      <c r="G72" s="3">
         <v>51900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>51600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>79100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>56200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>70000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>83700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>88700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>94500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>135900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>76300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>62000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>96200</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4527,8 +4701,11 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4592,8 +4769,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4657,8 +4837,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4722,56 +4905,59 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>542200</v>
+        <v>505100</v>
       </c>
       <c r="E76" s="3">
-        <v>514300</v>
+        <v>542500</v>
       </c>
       <c r="F76" s="3">
+        <v>514200</v>
+      </c>
+      <c r="G76" s="3">
         <v>540700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>538100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>552800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>514400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>533500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>573400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>564300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>388200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>430100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>370300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>57300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>89900</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4787,8 +4973,11 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4852,67 +5041,70 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4922,62 +5114,65 @@
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>15400</v>
+      </c>
+      <c r="E81" s="3">
         <v>47000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>18500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>35700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>19400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>46600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>12200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>15900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>18300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>13200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>21500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>73400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>14300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>15600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>46600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>18700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>39800</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4987,8 +5182,11 @@
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5012,8 +5210,9 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5035,39 +5234,39 @@
       <c r="I83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J83" s="3">
+      <c r="J83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K83" s="3">
         <v>5100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>5200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>8800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>3900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>5800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>2100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>6200</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5077,8 +5276,11 @@
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5142,8 +5344,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5207,8 +5412,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5272,8 +5480,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5337,8 +5548,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5402,8 +5616,11 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -5425,39 +5642,39 @@
       <c r="I89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J89" s="3">
+      <c r="J89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K89" s="3">
         <v>7700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>26300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>107600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>47800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>31700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>34600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-6600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>59300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-4200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>48600</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5467,8 +5684,11 @@
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5492,62 +5712,63 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1400</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-800</v>
       </c>
       <c r="I91" s="3">
         <v>-800</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>-800</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
       </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-200</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-200</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5557,8 +5778,11 @@
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5622,8 +5846,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5687,8 +5914,11 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5710,39 +5940,39 @@
       <c r="I94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J94" s="3">
+      <c r="J94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K94" s="3">
         <v>27900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-230900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-284200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>34800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-283200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-297400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>6500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>17000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-21000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>32300</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5752,8 +5982,11 @@
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5777,8 +6010,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5801,26 +6035,26 @@
         <v>0</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>-29700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-23600</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-119800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-63000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-37700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-23300</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
@@ -5842,8 +6076,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5907,8 +6144,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5972,8 +6212,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6037,8 +6280,11 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6060,39 +6306,39 @@
       <c r="I100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K100" s="3">
         <v>-30500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>201100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>177900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-63500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>262400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>277300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-25600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-40600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-53300</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6102,8 +6348,11 @@
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6125,29 +6374,29 @@
       <c r="I101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J101" s="3">
+      <c r="J101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K101" s="3">
         <v>-1500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1200</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
       <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>-100</v>
-      </c>
-      <c r="N101" s="3">
-        <v>200</v>
       </c>
       <c r="O101" s="3">
         <v>200</v>
       </c>
       <c r="P101" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Q101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="R101" s="3">
         <v>-100</v>
@@ -6155,8 +6404,8 @@
       <c r="S101" s="3">
         <v>-100</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>3</v>
+      <c r="T101" s="3">
+        <v>-100</v>
       </c>
       <c r="U101" s="3" t="s">
         <v>3</v>
@@ -6167,8 +6416,11 @@
       <c r="W101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -6190,39 +6442,39 @@
       <c r="I102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J102" s="3">
+      <c r="J102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K102" s="3">
         <v>3500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>19100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>11100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>14700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-25600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>35600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-25800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>27600</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6230,6 +6482,9 @@
         <v>3</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PAX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PAX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="92">
   <si>
     <t>PAX</t>
   </si>
@@ -656,95 +656,96 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
@@ -754,65 +755,68 @@
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>75000</v>
+      </c>
+      <c r="E8" s="3">
         <v>63900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>111900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>64500</v>
       </c>
-      <c r="G8" s="3">
-        <v>78600</v>
-      </c>
       <c r="H8" s="3">
-        <v>73800</v>
+        <v>79100</v>
       </c>
       <c r="I8" s="3">
+        <v>73900</v>
+      </c>
+      <c r="J8" s="3">
         <v>91300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>57000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>55600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>55000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>46200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>39700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>119000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>30600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>31800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>83300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>35200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>88000</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
@@ -822,65 +826,68 @@
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>39500</v>
+      </c>
+      <c r="E9" s="3">
         <v>26900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>50100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>28000</v>
       </c>
-      <c r="G9" s="3">
-        <v>35900</v>
-      </c>
       <c r="H9" s="3">
-        <v>34800</v>
+        <v>36800</v>
       </c>
       <c r="I9" s="3">
+        <v>34900</v>
+      </c>
+      <c r="J9" s="3">
         <v>40800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>26000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>27400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>27600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>16400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>15200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>43100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>12000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>7200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>26000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>8700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>34200</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
@@ -890,65 +897,68 @@
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>35500</v>
+      </c>
+      <c r="E10" s="3">
         <v>37000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>61800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>36500</v>
       </c>
-      <c r="G10" s="3">
-        <v>42700</v>
-      </c>
       <c r="H10" s="3">
+        <v>42300</v>
+      </c>
+      <c r="I10" s="3">
         <v>39000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>50500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>31000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>28200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>27400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>29800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>24500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>75900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>18600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>24600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>57300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>26500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>53800</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
@@ -958,8 +968,11 @@
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -984,8 +997,9 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1052,8 +1066,11 @@
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1120,56 +1137,59 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>6100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2600</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
+      <c r="H14" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I14" s="3">
+        <v>1900</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>5100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>8900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>100</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>2400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>2200</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1179,8 +1199,8 @@
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1188,40 +1208,43 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F15" s="3">
         <v>1100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1300</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>3</v>
+      <c r="H15" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I15" s="3">
+        <v>1100</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K15" s="3">
+      <c r="K15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L15" s="3">
         <v>1800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1600</v>
-      </c>
-      <c r="M15" s="3">
-        <v>500</v>
       </c>
       <c r="N15" s="3">
         <v>500</v>
@@ -1233,20 +1256,20 @@
         <v>500</v>
       </c>
       <c r="Q15" s="3">
+        <v>500</v>
+      </c>
+      <c r="R15" s="3">
         <v>400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>1300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>1700</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1256,8 +1279,11 @@
       <c r="X15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1279,65 +1305,66 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>67100</v>
+      </c>
+      <c r="E17" s="3">
         <v>43100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>53300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>45000</v>
       </c>
-      <c r="G17" s="3">
-        <v>51000</v>
-      </c>
       <c r="H17" s="3">
-        <v>52100</v>
+        <v>50100</v>
       </c>
       <c r="I17" s="3">
+        <v>62400</v>
+      </c>
+      <c r="J17" s="3">
         <v>44400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>40900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>42100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>37100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>31700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>18300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>46900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>16800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>15100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>34700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>14600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>44000</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1347,65 +1374,68 @@
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E18" s="3">
         <v>20800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>58600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>19500</v>
       </c>
-      <c r="G18" s="3">
-        <v>27600</v>
-      </c>
       <c r="H18" s="3">
-        <v>21700</v>
+        <v>29000</v>
       </c>
       <c r="I18" s="3">
+        <v>11500</v>
+      </c>
+      <c r="J18" s="3">
         <v>46900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>16100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>13500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>17900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>14500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>21400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>72100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>13800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>16700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>48600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>20600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>44000</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1415,8 +1445,11 @@
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1441,65 +1474,66 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="E20" s="3">
         <v>-800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-7700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I20" s="3">
+        <v>9600</v>
+      </c>
+      <c r="J20" s="3">
+        <v>2100</v>
+      </c>
+      <c r="K20" s="3">
+        <v>-700</v>
+      </c>
+      <c r="L20" s="3">
+        <v>2700</v>
+      </c>
+      <c r="M20" s="3">
+        <v>5200</v>
+      </c>
+      <c r="N20" s="3">
         <v>800</v>
       </c>
-      <c r="H20" s="3">
-        <v>1300</v>
-      </c>
-      <c r="I20" s="3">
-        <v>2100</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-700</v>
-      </c>
-      <c r="K20" s="3">
-        <v>2700</v>
-      </c>
-      <c r="L20" s="3">
-        <v>5200</v>
-      </c>
-      <c r="M20" s="3">
-        <v>800</v>
-      </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>400</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>600</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>900</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1509,8 +1543,11 @@
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1520,54 +1557,54 @@
       <c r="E21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
+      <c r="F21" s="3">
+        <v>58200</v>
+      </c>
+      <c r="G21" s="3">
+        <v>38500</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K21" s="3">
+      <c r="I21" s="3">
+        <v>5800</v>
+      </c>
+      <c r="J21" s="3">
+        <v>70200</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L21" s="3">
         <v>21300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>28300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>24100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>22900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>76400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>15800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>18600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>55000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>22700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>51100</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1577,40 +1614,43 @@
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E22" s="3">
-        <v>300</v>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F22" s="3">
         <v>300</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
+      <c r="G22" s="3">
+        <v>300</v>
+      </c>
+      <c r="H22" s="3">
+        <v>300</v>
+      </c>
+      <c r="I22" s="3">
+        <v>300</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
+      <c r="K22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L22" s="3">
         <v>700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>600</v>
-      </c>
-      <c r="M22" s="3">
-        <v>300</v>
       </c>
       <c r="N22" s="3">
         <v>300</v>
@@ -1622,20 +1662,20 @@
         <v>300</v>
       </c>
       <c r="Q22" s="3">
+        <v>300</v>
+      </c>
+      <c r="R22" s="3">
         <v>200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>800</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1645,65 +1685,68 @@
       <c r="X22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E23" s="3">
         <v>20000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>50700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>18300</v>
       </c>
-      <c r="G23" s="3">
-        <v>28400</v>
-      </c>
       <c r="H23" s="3">
-        <v>23000</v>
+        <v>28300</v>
       </c>
       <c r="I23" s="3">
+        <v>20700</v>
+      </c>
+      <c r="J23" s="3">
         <v>49000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>15400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>15600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>22500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>15100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>20700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>72200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>13600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>16500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>48500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>20300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>44100</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1713,65 +1756,68 @@
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>600</v>
+      </c>
+      <c r="E24" s="3">
         <v>4200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-7700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3100</v>
-      </c>
-      <c r="I24" s="3">
-        <v>2200</v>
       </c>
       <c r="J24" s="3">
         <v>2200</v>
       </c>
       <c r="K24" s="3">
+        <v>2200</v>
+      </c>
+      <c r="L24" s="3">
         <v>-300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>4200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-1200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>3000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>2700</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1781,8 +1827,11 @@
       <c r="X24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1849,65 +1898,68 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E26" s="3">
         <v>15800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>48400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>18800</v>
       </c>
-      <c r="G26" s="3">
-        <v>36100</v>
-      </c>
       <c r="H26" s="3">
-        <v>19900</v>
+        <v>36000</v>
       </c>
       <c r="I26" s="3">
+        <v>17600</v>
+      </c>
+      <c r="J26" s="3">
         <v>46700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>13200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>15900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>18300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>13200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>21500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>73400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>13100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>16300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>45500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>19600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>41400</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1917,65 +1969,68 @@
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>800</v>
+      </c>
+      <c r="E27" s="3">
         <v>15400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>47000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>18500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>35700</v>
       </c>
-      <c r="H27" s="3">
-        <v>19400</v>
-      </c>
       <c r="I27" s="3">
+        <v>17200</v>
+      </c>
+      <c r="J27" s="3">
         <v>46600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>12200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>15900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>18300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>13200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>21500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>73400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>14300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>15600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>46600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>18700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>39800</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1985,8 +2040,11 @@
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2053,8 +2111,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2121,8 +2182,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2189,8 +2253,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2257,65 +2324,68 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E32" s="3">
         <v>800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>7700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
+        <v>400</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="K32" s="3">
+        <v>700</v>
+      </c>
+      <c r="L32" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="M32" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="N32" s="3">
         <v>-800</v>
       </c>
-      <c r="H32" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="J32" s="3">
-        <v>700</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-5200</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-800</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-400</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-600</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-900</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2325,65 +2395,68 @@
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>800</v>
+      </c>
+      <c r="E33" s="3">
         <v>15400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>47000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>18500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>35700</v>
       </c>
-      <c r="H33" s="3">
-        <v>19400</v>
-      </c>
       <c r="I33" s="3">
+        <v>17200</v>
+      </c>
+      <c r="J33" s="3">
         <v>46600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>12200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>15900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>18300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>13200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>21500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>73400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>14300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>15600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>46600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>18700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>39800</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2393,8 +2466,11 @@
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2461,65 +2537,68 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>800</v>
+      </c>
+      <c r="E35" s="3">
         <v>15400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>47000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>18500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>35700</v>
       </c>
-      <c r="H35" s="3">
-        <v>19400</v>
-      </c>
       <c r="I35" s="3">
+        <v>17200</v>
+      </c>
+      <c r="J35" s="3">
         <v>46600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>12200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>15900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>18300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>13200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>21500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>73400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>14300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>15600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>46600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>18700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>39800</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2529,70 +2608,73 @@
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2602,8 +2684,11 @@
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2628,8 +2713,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2654,59 +2740,60 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>28900</v>
+      </c>
+      <c r="E41" s="3">
         <v>17300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>12000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>12800</v>
       </c>
-      <c r="G41" s="3">
-        <v>22400</v>
-      </c>
       <c r="H41" s="3">
-        <v>30800</v>
+        <v>16400</v>
       </c>
       <c r="I41" s="3">
+        <v>22600</v>
+      </c>
+      <c r="J41" s="3">
         <v>21400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>24400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>13400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>12900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>15300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>44300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>25200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>28700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>14100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>39700</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2722,59 +2809,62 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>70100</v>
+      </c>
+      <c r="E42" s="3">
         <v>197600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>208500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>210200</v>
       </c>
-      <c r="G42" s="3">
-        <v>205600</v>
-      </c>
       <c r="H42" s="3">
-        <v>253400</v>
+        <v>211600</v>
       </c>
       <c r="I42" s="3">
+        <v>261500</v>
+      </c>
+      <c r="J42" s="3">
         <v>291000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>317000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>328400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>136000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>151900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>250800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>286300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>300400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>9900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>11600</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2790,59 +2880,62 @@
       <c r="X42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>139400</v>
+      </c>
+      <c r="E43" s="3">
         <v>142400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>152200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>130100</v>
       </c>
-      <c r="G43" s="3">
-        <v>120600</v>
-      </c>
       <c r="H43" s="3">
-        <v>151900</v>
+        <v>122400</v>
       </c>
       <c r="I43" s="3">
+        <v>153200</v>
+      </c>
+      <c r="J43" s="3">
         <v>137900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>95900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>95600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>105400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>103500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>122300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>113700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>24400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>26000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>10000</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2858,8 +2951,11 @@
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2926,59 +3022,62 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>64900</v>
+      </c>
+      <c r="E45" s="3">
         <v>89500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>28800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>19200</v>
       </c>
-      <c r="G45" s="3">
-        <v>29200</v>
-      </c>
       <c r="H45" s="3">
-        <v>28100</v>
+        <v>27400</v>
       </c>
       <c r="I45" s="3">
+        <v>25000</v>
+      </c>
+      <c r="J45" s="3">
         <v>29300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>51600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>55500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>83900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>81700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1800</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2994,59 +3093,62 @@
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>303300</v>
+      </c>
+      <c r="E46" s="3">
         <v>446800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>401600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>372400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>377800</v>
       </c>
-      <c r="H46" s="3">
-        <v>464200</v>
-      </c>
       <c r="I46" s="3">
+        <v>462300</v>
+      </c>
+      <c r="J46" s="3">
         <v>479600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>488900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>492900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>338200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>352300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>421400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>428200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>355500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>53700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>63100</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3062,59 +3164,62 @@
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>65900</v>
+      </c>
+      <c r="E47" s="3">
         <v>74200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>75500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>72900</v>
       </c>
-      <c r="G47" s="3">
-        <v>75700</v>
-      </c>
       <c r="H47" s="3">
-        <v>70000</v>
+        <v>75800</v>
       </c>
       <c r="I47" s="3">
+        <v>80100</v>
+      </c>
+      <c r="J47" s="3">
         <v>50400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>58600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>44100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>282900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>30000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>30600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>31100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>30400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>24500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>36500</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3130,59 +3235,62 @@
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>27700</v>
+      </c>
+      <c r="E48" s="3">
         <v>28800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>28200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>23800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>25400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>25200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>24600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>24000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>18300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>15800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>13400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3900</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3198,59 +3306,62 @@
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>693500</v>
+      </c>
+      <c r="E49" s="3">
         <v>473500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>487000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>438400</v>
       </c>
-      <c r="G49" s="3">
-        <v>452400</v>
-      </c>
       <c r="H49" s="3">
-        <v>417900</v>
+        <v>451000</v>
       </c>
       <c r="I49" s="3">
+        <v>422600</v>
+      </c>
+      <c r="J49" s="3">
         <v>411500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>359500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>339800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>366300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>358900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>18300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>19300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>21400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>22400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>23700</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3266,8 +3377,11 @@
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3334,8 +3448,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3402,59 +3519,62 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>86500</v>
+      </c>
+      <c r="E52" s="3">
         <v>21100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>19300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>22100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>19500</v>
       </c>
-      <c r="H52" s="3">
-        <v>21700</v>
-      </c>
       <c r="I52" s="3">
+        <v>9600</v>
+      </c>
+      <c r="J52" s="3">
         <v>10000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>5700</v>
-      </c>
-      <c r="K52" s="3">
-        <v>5500</v>
       </c>
       <c r="L52" s="3">
         <v>5500</v>
       </c>
       <c r="M52" s="3">
+        <v>5500</v>
+      </c>
+      <c r="N52" s="3">
         <v>6700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2800</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3470,8 +3590,11 @@
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3538,59 +3661,62 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1176900</v>
+      </c>
+      <c r="E54" s="3">
         <v>1044400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1011600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>929600</v>
       </c>
-      <c r="G54" s="3">
-        <v>950800</v>
-      </c>
       <c r="H54" s="3">
-        <v>999000</v>
+        <v>949400</v>
       </c>
       <c r="I54" s="3">
+        <v>999800</v>
+      </c>
+      <c r="J54" s="3">
         <v>976200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>936700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>900700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1008700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>761300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>478500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>486400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>413500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>107200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>130000</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3606,8 +3732,11 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3632,8 +3761,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3658,8 +3788,9 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3726,59 +3857,62 @@
       <c r="X57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>28300</v>
+      </c>
+      <c r="E58" s="3">
         <v>10000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2900</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
+      <c r="H58" s="3">
+        <v>2900</v>
       </c>
       <c r="I58" s="3">
+        <v>2600</v>
+      </c>
+      <c r="J58" s="3">
         <v>2200</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K58" s="3">
+      <c r="K58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L58" s="3">
         <v>1200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>700</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3794,59 +3928,62 @@
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>340400</v>
+      </c>
+      <c r="E59" s="3">
         <v>384400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>394500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>313100</v>
       </c>
-      <c r="G59" s="3">
-        <v>280700</v>
-      </c>
       <c r="H59" s="3">
-        <v>371200</v>
+        <v>278300</v>
       </c>
       <c r="I59" s="3">
+        <v>362800</v>
+      </c>
+      <c r="J59" s="3">
         <v>335800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>347600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>312600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>164600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>155300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>84700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>51400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>38600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>43300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>33900</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3862,59 +3999,62 @@
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>368700</v>
+      </c>
+      <c r="E60" s="3">
         <v>394400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>397500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>316000</v>
       </c>
-      <c r="G60" s="3">
-        <v>280700</v>
-      </c>
       <c r="H60" s="3">
-        <v>371200</v>
+        <v>281200</v>
       </c>
       <c r="I60" s="3">
+        <v>365400</v>
+      </c>
+      <c r="J60" s="3">
         <v>338000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>347600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>313900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>166200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>156200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>85600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>52400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>39500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>44000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>34600</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3930,59 +4070,62 @@
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>148800</v>
+      </c>
+      <c r="E61" s="3">
         <v>73400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>12800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>12700</v>
       </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>14100</v>
       </c>
       <c r="I61" s="3">
+        <v>14200</v>
+      </c>
+      <c r="J61" s="3">
         <v>13900</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>8800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>900</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -3998,59 +4141,62 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>159200</v>
+      </c>
+      <c r="E62" s="3">
         <v>88100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>79900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>127500</v>
       </c>
-      <c r="G62" s="3">
-        <v>161300</v>
-      </c>
       <c r="H62" s="3">
-        <v>131800</v>
+        <v>146900</v>
       </c>
       <c r="I62" s="3">
+        <v>125700</v>
+      </c>
+      <c r="J62" s="3">
         <v>110900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>73500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>44500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>261900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>33900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3900</v>
-      </c>
-      <c r="O62" s="3">
-        <v>2900</v>
       </c>
       <c r="P62" s="3">
         <v>2900</v>
       </c>
       <c r="Q62" s="3">
+        <v>2900</v>
+      </c>
+      <c r="R62" s="3">
         <v>3300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4400</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4066,8 +4212,11 @@
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4134,8 +4283,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4202,8 +4354,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4270,59 +4425,62 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>663700</v>
+      </c>
+      <c r="E66" s="3">
         <v>539300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>469100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>415500</v>
       </c>
-      <c r="G66" s="3">
-        <v>410100</v>
-      </c>
       <c r="H66" s="3">
-        <v>460900</v>
+        <v>398300</v>
       </c>
       <c r="I66" s="3">
+        <v>460600</v>
+      </c>
+      <c r="J66" s="3">
         <v>423500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>422300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>367200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>435300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>197000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>90300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>56300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>43200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>49900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>40100</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4338,8 +4496,11 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4364,8 +4525,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4432,8 +4594,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4500,8 +4665,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4568,8 +4736,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4636,59 +4807,62 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-19500</v>
+      </c>
+      <c r="E72" s="3">
         <v>8400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>53800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>35700</v>
       </c>
-      <c r="G72" s="3">
-        <v>51900</v>
-      </c>
       <c r="H72" s="3">
-        <v>51600</v>
+        <v>54200</v>
       </c>
       <c r="I72" s="3">
+        <v>51200</v>
+      </c>
+      <c r="J72" s="3">
         <v>79100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>56200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>70000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>83700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>88700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>94500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>135900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>76300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>62000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>96200</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4704,8 +4878,11 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4772,8 +4949,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4840,8 +5020,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4908,59 +5091,62 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>513200</v>
+      </c>
+      <c r="E76" s="3">
         <v>505100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>542500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>514200</v>
       </c>
-      <c r="G76" s="3">
-        <v>540700</v>
-      </c>
       <c r="H76" s="3">
-        <v>538100</v>
+        <v>551100</v>
       </c>
       <c r="I76" s="3">
+        <v>539200</v>
+      </c>
+      <c r="J76" s="3">
         <v>552800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>514400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>533500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>573400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>564300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>388200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>430100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>370300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>57300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>89900</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4976,8 +5162,11 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5044,70 +5233,73 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5117,65 +5309,68 @@
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>800</v>
+      </c>
+      <c r="E81" s="3">
         <v>15400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>47000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>18500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>35700</v>
       </c>
-      <c r="H81" s="3">
-        <v>19400</v>
-      </c>
       <c r="I81" s="3">
+        <v>17200</v>
+      </c>
+      <c r="J81" s="3">
         <v>46600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>12200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>15900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>18300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>13200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>21500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>73400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>14300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>15600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>46600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>18700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>39800</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5185,8 +5380,11 @@
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5211,8 +5409,9 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5222,54 +5421,54 @@
       <c r="E83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
+      <c r="F83" s="3">
+        <v>7200</v>
+      </c>
+      <c r="G83" s="3">
+        <v>19900</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="I83" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="J83" s="3">
+        <v>21200</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L83" s="3">
         <v>5100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>5200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>8800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>3900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>5800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>2100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>6200</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5279,8 +5478,11 @@
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5347,8 +5549,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5415,8 +5620,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5483,8 +5691,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5551,8 +5762,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5619,8 +5833,11 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -5630,54 +5847,54 @@
       <c r="E89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>3</v>
+      <c r="F89" s="3">
+        <v>39400</v>
+      </c>
+      <c r="G89" s="3">
+        <v>117300</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K89" s="3">
+      <c r="I89" s="3">
+        <v>-51800</v>
+      </c>
+      <c r="J89" s="3">
+        <v>81100</v>
+      </c>
+      <c r="K89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L89" s="3">
         <v>7700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>26300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>107600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>47800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>31700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>34600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-6600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>59300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-4200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>48600</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5687,8 +5904,11 @@
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5713,8 +5933,9 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5722,56 +5943,56 @@
         <v>-5000</v>
       </c>
       <c r="E91" s="3">
-        <v>-1900</v>
+        <v>-900</v>
       </c>
       <c r="F91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="G91" s="3">
+        <v>-600</v>
+      </c>
+      <c r="H91" s="3">
         <v>-2200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-3100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-1400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-800</v>
       </c>
-      <c r="J91" s="3">
-        <v>-800</v>
-      </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-200</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-200</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
         <v>-100</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5781,8 +6002,11 @@
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5849,8 +6073,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5917,8 +6144,11 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5928,54 +6158,54 @@
       <c r="E94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
+      <c r="F94" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="G94" s="3">
+        <v>70800</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K94" s="3">
+      <c r="I94" s="3">
+        <v>210600</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-189300</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L94" s="3">
         <v>27900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-230900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-284200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>34800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-283200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-297400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>6500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>17000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-21000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>32300</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5985,8 +6215,11 @@
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6011,8 +6244,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6023,41 +6257,41 @@
         <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>-29400</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>-115700</v>
       </c>
       <c r="H96" s="3">
         <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>58000</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>-103300</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>-29700</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-23600</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-119800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-63000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-37700</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-23300</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
@@ -6079,8 +6313,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6147,8 +6384,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6215,8 +6455,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6283,8 +6526,11 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6294,54 +6540,54 @@
       <c r="E100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
+      <c r="F100" s="3">
+        <v>-32600</v>
+      </c>
+      <c r="G100" s="3">
+        <v>-197000</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K100" s="3">
+      <c r="I100" s="3">
+        <v>-165700</v>
+      </c>
+      <c r="J100" s="3">
+        <v>118500</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L100" s="3">
         <v>-30500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>201100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>177900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-63500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>262400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>277300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-25600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-40600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-53300</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6351,8 +6597,11 @@
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6362,44 +6611,44 @@
       <c r="E101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>3</v>
+      <c r="F101" s="3">
+        <v>300</v>
+      </c>
+      <c r="G101" s="3">
+        <v>0</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K101" s="3">
+      <c r="I101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3">
         <v>-1500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1200</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
       <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
         <v>-100</v>
-      </c>
-      <c r="O101" s="3">
-        <v>200</v>
       </c>
       <c r="P101" s="3">
         <v>200</v>
       </c>
       <c r="Q101" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="R101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="S101" s="3">
         <v>-100</v>
@@ -6407,8 +6656,8 @@
       <c r="T101" s="3">
         <v>-100</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>3</v>
+      <c r="U101" s="3">
+        <v>-100</v>
       </c>
       <c r="V101" s="3" t="s">
         <v>3</v>
@@ -6419,8 +6668,11 @@
       <c r="X101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -6430,54 +6682,54 @@
       <c r="E102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>3</v>
+      <c r="F102" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="G102" s="3">
+        <v>-9000</v>
       </c>
       <c r="H102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K102" s="3">
+      <c r="I102" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="J102" s="3">
+        <v>11300</v>
+      </c>
+      <c r="K102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L102" s="3">
         <v>3500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>19100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>11100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>14700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-25600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>35600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-25800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>27600</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6485,6 +6737,9 @@
         <v>3</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PAX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PAX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="92">
   <si>
     <t>PAX</t>
   </si>
@@ -656,99 +656,100 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
@@ -758,68 +759,71 @@
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>78000</v>
+      </c>
+      <c r="E8" s="3">
         <v>75000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>63900</v>
       </c>
-      <c r="F8" s="3">
-        <v>111900</v>
-      </c>
       <c r="G8" s="3">
-        <v>64500</v>
+        <v>111700</v>
       </c>
       <c r="H8" s="3">
-        <v>79100</v>
+        <v>63500</v>
       </c>
       <c r="I8" s="3">
-        <v>73900</v>
+        <v>78600</v>
       </c>
       <c r="J8" s="3">
+        <v>73800</v>
+      </c>
+      <c r="K8" s="3">
         <v>91300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>57000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>55600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>55000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>46200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>39700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>119000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>30600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>31800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>83300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>35200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>88000</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
@@ -829,68 +833,71 @@
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>39500</v>
+        <v>32900</v>
       </c>
       <c r="E9" s="3">
-        <v>26900</v>
+        <v>32400</v>
       </c>
       <c r="F9" s="3">
-        <v>50100</v>
+        <v>20800</v>
       </c>
       <c r="G9" s="3">
-        <v>28000</v>
+        <v>49400</v>
       </c>
       <c r="H9" s="3">
-        <v>36800</v>
+        <v>20200</v>
       </c>
       <c r="I9" s="3">
-        <v>34900</v>
+        <v>30400</v>
       </c>
       <c r="J9" s="3">
+        <v>29300</v>
+      </c>
+      <c r="K9" s="3">
         <v>40800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>26000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>27400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>27600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>16400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>15200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>43100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>12000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>7200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>26000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>8700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>34200</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
@@ -900,68 +907,71 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>35500</v>
+        <v>45100</v>
       </c>
       <c r="E10" s="3">
-        <v>37000</v>
+        <v>42600</v>
       </c>
       <c r="F10" s="3">
-        <v>61800</v>
+        <v>43100</v>
       </c>
       <c r="G10" s="3">
-        <v>36500</v>
+        <v>62300</v>
       </c>
       <c r="H10" s="3">
-        <v>42300</v>
+        <v>43300</v>
       </c>
       <c r="I10" s="3">
-        <v>39000</v>
+        <v>48200</v>
       </c>
       <c r="J10" s="3">
+        <v>44400</v>
+      </c>
+      <c r="K10" s="3">
         <v>50500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>31000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>28200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>27400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>29800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>24500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>75900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>18600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>24600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>57300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>26500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>53800</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
@@ -971,8 +981,11 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -998,8 +1011,9 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1069,8 +1083,11 @@
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1140,59 +1157,62 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3">
-        <v>6100</v>
+      <c r="E14" s="3">
+        <v>20500</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G14" s="3">
-        <v>2600</v>
+        <v>-12800</v>
       </c>
       <c r="H14" s="3">
-        <v>1200</v>
+        <v>1600</v>
       </c>
       <c r="I14" s="3">
-        <v>1900</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
+        <v>-2500</v>
+      </c>
+      <c r="J14" s="3">
+        <v>12700</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
         <v>5100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>8900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>100</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>2400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>2200</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1202,8 +1222,8 @@
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
@@ -1211,43 +1231,46 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>3</v>
+      <c r="D15" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E15" s="3">
+        <v>6400</v>
       </c>
       <c r="F15" s="3">
-        <v>1100</v>
+        <v>6100</v>
       </c>
       <c r="G15" s="3">
-        <v>1300</v>
+        <v>6100</v>
       </c>
       <c r="H15" s="3">
-        <v>1200</v>
+        <v>5900</v>
       </c>
       <c r="I15" s="3">
-        <v>1100</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>3</v>
+        <v>5500</v>
+      </c>
+      <c r="J15" s="3">
+        <v>4900</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L15" s="3">
+      <c r="L15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M15" s="3">
         <v>1800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1600</v>
-      </c>
-      <c r="N15" s="3">
-        <v>500</v>
       </c>
       <c r="O15" s="3">
         <v>500</v>
@@ -1259,20 +1282,20 @@
         <v>500</v>
       </c>
       <c r="R15" s="3">
+        <v>500</v>
+      </c>
+      <c r="S15" s="3">
         <v>400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>1300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>1700</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1282,8 +1305,11 @@
       <c r="Y15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1306,68 +1332,69 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>67100</v>
+        <v>65200</v>
       </c>
       <c r="E17" s="3">
+        <v>50000</v>
+      </c>
+      <c r="F17" s="3">
         <v>43100</v>
       </c>
-      <c r="F17" s="3">
-        <v>53300</v>
-      </c>
       <c r="G17" s="3">
-        <v>45000</v>
+        <v>59100</v>
       </c>
       <c r="H17" s="3">
-        <v>50100</v>
+        <v>39100</v>
       </c>
       <c r="I17" s="3">
-        <v>62400</v>
+        <v>46000</v>
       </c>
       <c r="J17" s="3">
+        <v>43200</v>
+      </c>
+      <c r="K17" s="3">
         <v>44400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>40900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>42100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>37100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>31700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>18300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>46900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>16800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>15100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>34700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>14600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>44000</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1377,68 +1404,71 @@
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>7900</v>
+        <v>12800</v>
       </c>
       <c r="E18" s="3">
+        <v>25000</v>
+      </c>
+      <c r="F18" s="3">
         <v>20800</v>
       </c>
-      <c r="F18" s="3">
-        <v>58600</v>
-      </c>
       <c r="G18" s="3">
-        <v>19500</v>
+        <v>52600</v>
       </c>
       <c r="H18" s="3">
-        <v>29000</v>
+        <v>24500</v>
       </c>
       <c r="I18" s="3">
-        <v>11500</v>
+        <v>32500</v>
       </c>
       <c r="J18" s="3">
+        <v>30600</v>
+      </c>
+      <c r="K18" s="3">
         <v>46900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>16100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>13500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>17900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>14500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>21400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>72100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>13800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>16700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>48600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>20600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>44000</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1448,8 +1478,11 @@
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1475,68 +1508,69 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-4800</v>
+        <v>200</v>
       </c>
       <c r="E20" s="3">
-        <v>-800</v>
+        <v>1000</v>
       </c>
       <c r="F20" s="3">
-        <v>-7700</v>
+        <v>200</v>
       </c>
       <c r="G20" s="3">
-        <v>-900</v>
+        <v>14500</v>
       </c>
       <c r="H20" s="3">
-        <v>-400</v>
+        <v>4200</v>
       </c>
       <c r="I20" s="3">
-        <v>9600</v>
+        <v>6400</v>
       </c>
       <c r="J20" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="K20" s="3">
         <v>2100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>5200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>400</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>600</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>900</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1546,68 +1580,71 @@
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>18900</v>
+      </c>
+      <c r="E21" s="3">
+        <v>30400</v>
       </c>
       <c r="F21" s="3">
-        <v>58200</v>
+        <v>26700</v>
       </c>
       <c r="G21" s="3">
-        <v>38500</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
+        <v>44200</v>
+      </c>
+      <c r="H21" s="3">
+        <v>26100</v>
       </c>
       <c r="I21" s="3">
-        <v>5800</v>
+        <v>31600</v>
       </c>
       <c r="J21" s="3">
+        <v>38600</v>
+      </c>
+      <c r="K21" s="3">
         <v>70200</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3">
         <v>21300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>28300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>24100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>22900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>76400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>15800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>18600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>55000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>22700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>51100</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1617,19 +1654,22 @@
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>3</v>
+      <c r="D22" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E22" s="3">
+        <v>400</v>
       </c>
       <c r="F22" s="3">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="G22" s="3">
         <v>300</v>
@@ -1640,20 +1680,20 @@
       <c r="I22" s="3">
         <v>300</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
+      <c r="J22" s="3">
+        <v>300</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
+      <c r="L22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M22" s="3">
         <v>700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>600</v>
-      </c>
-      <c r="N22" s="3">
-        <v>300</v>
       </c>
       <c r="O22" s="3">
         <v>300</v>
@@ -1665,20 +1705,20 @@
         <v>300</v>
       </c>
       <c r="R22" s="3">
+        <v>300</v>
+      </c>
+      <c r="S22" s="3">
         <v>200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>800</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1688,68 +1728,71 @@
       <c r="Y22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>3100</v>
+        <v>11200</v>
       </c>
       <c r="E23" s="3">
+        <v>3200</v>
+      </c>
+      <c r="F23" s="3">
         <v>20000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>50700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>18300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>28300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>20700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>49000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>15400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>15600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>22500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>15100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>20700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>72200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>13600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>16500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>48500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>20300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>44100</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1759,68 +1802,71 @@
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E24" s="3">
         <v>600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-7700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3100</v>
-      </c>
-      <c r="J24" s="3">
-        <v>2200</v>
       </c>
       <c r="K24" s="3">
         <v>2200</v>
       </c>
       <c r="L24" s="3">
+        <v>2200</v>
+      </c>
+      <c r="M24" s="3">
         <v>-300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>4200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>3000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2700</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1830,8 +1876,11 @@
       <c r="Y24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1901,68 +1950,71 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E26" s="3">
         <v>2500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>15800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>48400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>18800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>36000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>17600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>46700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>13200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>15900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>18300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>13200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>21500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>73400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>13100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>16300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>45500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>19600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>41400</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1972,68 +2024,71 @@
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>800</v>
+        <v>1500</v>
       </c>
       <c r="E27" s="3">
+        <v>700</v>
+      </c>
+      <c r="F27" s="3">
         <v>15400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>47000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>18500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>35700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>17200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>46600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>12200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>15900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>18300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>13200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>21500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>73400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>14300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>15600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>46600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>18700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>39800</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2043,8 +2098,11 @@
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2114,8 +2172,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2185,8 +2246,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2256,8 +2320,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2327,68 +2394,71 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>4800</v>
+        <v>-200</v>
       </c>
       <c r="E32" s="3">
-        <v>800</v>
+        <v>-1000</v>
       </c>
       <c r="F32" s="3">
-        <v>7700</v>
+        <v>-200</v>
       </c>
       <c r="G32" s="3">
-        <v>900</v>
+        <v>-14500</v>
       </c>
       <c r="H32" s="3">
-        <v>400</v>
+        <v>-4200</v>
       </c>
       <c r="I32" s="3">
-        <v>-9600</v>
+        <v>-6400</v>
       </c>
       <c r="J32" s="3">
+        <v>3200</v>
+      </c>
+      <c r="K32" s="3">
         <v>-2100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-5200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-400</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-600</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-900</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2398,68 +2468,71 @@
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>800</v>
+        <v>1500</v>
       </c>
       <c r="E33" s="3">
+        <v>700</v>
+      </c>
+      <c r="F33" s="3">
         <v>15400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>47000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>18500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>35700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>17200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>46600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>12200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>15900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>18300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>13200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>21500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>73400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>14300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>15600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>46600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>18700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>39800</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2469,8 +2542,11 @@
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2540,68 +2616,71 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>800</v>
+        <v>1500</v>
       </c>
       <c r="E35" s="3">
+        <v>700</v>
+      </c>
+      <c r="F35" s="3">
         <v>15400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>47000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>18500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>35700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>17200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>46600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>12200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>15900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>18300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>13200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>21500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>73400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>14300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>15600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>46600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>18700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>39800</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2611,73 +2690,76 @@
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2687,8 +2769,11 @@
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2714,8 +2799,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2741,62 +2827,63 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>38300</v>
+      </c>
+      <c r="E41" s="3">
         <v>28900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>17300</v>
       </c>
-      <c r="F41" s="3">
-        <v>12000</v>
-      </c>
       <c r="G41" s="3">
-        <v>12800</v>
+        <v>16100</v>
       </c>
       <c r="H41" s="3">
-        <v>16400</v>
+        <v>17500</v>
       </c>
       <c r="I41" s="3">
-        <v>22600</v>
+        <v>22400</v>
       </c>
       <c r="J41" s="3">
+        <v>30800</v>
+      </c>
+      <c r="K41" s="3">
         <v>21400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>24400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>13400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>12900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>15300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>44300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>25200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>28700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>14100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>39700</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2812,62 +2899,65 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>70100</v>
+        <v>62900</v>
       </c>
       <c r="E42" s="3">
+        <v>17800</v>
+      </c>
+      <c r="F42" s="3">
         <v>197600</v>
       </c>
-      <c r="F42" s="3">
-        <v>208500</v>
-      </c>
       <c r="G42" s="3">
-        <v>210200</v>
+        <v>17200</v>
       </c>
       <c r="H42" s="3">
-        <v>211600</v>
+        <v>21600</v>
       </c>
       <c r="I42" s="3">
-        <v>261500</v>
+        <v>24900</v>
       </c>
       <c r="J42" s="3">
+        <v>10500</v>
+      </c>
+      <c r="K42" s="3">
         <v>291000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>317000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>328400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>136000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>151900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>250800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>286300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>300400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>9900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>11600</v>
       </c>
-      <c r="T42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2883,62 +2973,65 @@
       <c r="Y42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>139400</v>
+        <v>124000</v>
       </c>
       <c r="E43" s="3">
-        <v>142400</v>
+        <v>126300</v>
       </c>
       <c r="F43" s="3">
-        <v>152200</v>
+        <v>127100</v>
       </c>
       <c r="G43" s="3">
-        <v>130100</v>
+        <v>134600</v>
       </c>
       <c r="H43" s="3">
-        <v>122400</v>
+        <v>118900</v>
       </c>
       <c r="I43" s="3">
-        <v>153200</v>
+        <v>115700</v>
       </c>
       <c r="J43" s="3">
+        <v>147600</v>
+      </c>
+      <c r="K43" s="3">
         <v>137900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>95900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>95600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>105400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>103500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>122300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>113700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>24400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>26000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>10000</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2954,31 +3047,34 @@
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3025,62 +3121,65 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>64900</v>
+        <v>205700</v>
       </c>
       <c r="E45" s="3">
-        <v>89500</v>
+        <v>152700</v>
       </c>
       <c r="F45" s="3">
-        <v>28800</v>
+        <v>104800</v>
       </c>
       <c r="G45" s="3">
-        <v>19200</v>
+        <v>227700</v>
       </c>
       <c r="H45" s="3">
-        <v>27400</v>
+        <v>208000</v>
       </c>
       <c r="I45" s="3">
-        <v>25000</v>
+        <v>210600</v>
       </c>
       <c r="J45" s="3">
+        <v>269100</v>
+      </c>
+      <c r="K45" s="3">
         <v>29300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>51600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>55500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>83900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>81700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1800</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3096,62 +3195,65 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>303300</v>
+        <v>430900</v>
       </c>
       <c r="E46" s="3">
+        <v>333800</v>
+      </c>
+      <c r="F46" s="3">
         <v>446800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>401600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>372400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>377800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>462300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>479600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>488900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>492900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>338200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>352300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>421400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>428200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>355500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>53700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>63100</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3167,62 +3269,65 @@
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>65900</v>
+        <v>48400</v>
       </c>
       <c r="E47" s="3">
-        <v>74200</v>
+        <v>49300</v>
       </c>
       <c r="F47" s="3">
-        <v>75500</v>
+        <v>52600</v>
       </c>
       <c r="G47" s="3">
-        <v>72900</v>
+        <v>58600</v>
       </c>
       <c r="H47" s="3">
-        <v>75800</v>
+        <v>54100</v>
       </c>
       <c r="I47" s="3">
-        <v>80100</v>
+        <v>55200</v>
       </c>
       <c r="J47" s="3">
+        <v>62700</v>
+      </c>
+      <c r="K47" s="3">
         <v>50400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>58600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>44100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>282900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>30000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>30600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>31100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>30400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>24500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>36500</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3238,62 +3343,65 @@
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>26500</v>
+      </c>
+      <c r="E48" s="3">
         <v>27700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>28800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>28200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>23800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>25400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>25200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>24600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>24000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>18300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>15800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>13400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3900</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3309,62 +3417,65 @@
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>693500</v>
+        <v>740300</v>
       </c>
       <c r="E49" s="3">
+        <v>712600</v>
+      </c>
+      <c r="F49" s="3">
         <v>473500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>487000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>438400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>451000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>422600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>411500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>359500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>339800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>366300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>358900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>18300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>19300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>21400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>22400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>23700</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3380,8 +3491,11 @@
       <c r="Y49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3451,8 +3565,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3522,62 +3639,65 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>86500</v>
+        <v>45500</v>
       </c>
       <c r="E52" s="3">
-        <v>21100</v>
+        <v>25900</v>
       </c>
       <c r="F52" s="3">
-        <v>19300</v>
+        <v>7100</v>
       </c>
       <c r="G52" s="3">
-        <v>22100</v>
+        <v>4500</v>
       </c>
       <c r="H52" s="3">
-        <v>19500</v>
+        <v>9000</v>
       </c>
       <c r="I52" s="3">
-        <v>9600</v>
+        <v>9900</v>
       </c>
       <c r="J52" s="3">
+        <v>10700</v>
+      </c>
+      <c r="K52" s="3">
         <v>10000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5700</v>
-      </c>
-      <c r="L52" s="3">
-        <v>5500</v>
       </c>
       <c r="M52" s="3">
         <v>5500</v>
       </c>
       <c r="N52" s="3">
+        <v>5500</v>
+      </c>
+      <c r="O52" s="3">
         <v>6700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2800</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3593,8 +3713,11 @@
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3664,62 +3787,65 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1176900</v>
+        <v>1324400</v>
       </c>
       <c r="E54" s="3">
+        <v>1182000</v>
+      </c>
+      <c r="F54" s="3">
         <v>1044400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1011600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>929600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>949400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>999800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>976200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>936700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>900700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1008700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>761300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>478500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>486400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>413500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>107200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>130000</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3735,8 +3861,11 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3762,8 +3891,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3789,31 +3919,32 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>0</v>
+      <c r="D57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E57" s="3">
-        <v>0</v>
-      </c>
-      <c r="F57" s="3">
-        <v>0</v>
+        <v>12200</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G57" s="3">
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="H57" s="3">
-        <v>0</v>
+        <v>7100</v>
       </c>
       <c r="I57" s="3">
-        <v>0</v>
+        <v>4100</v>
       </c>
       <c r="J57" s="3">
-        <v>0</v>
+        <v>5100</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
@@ -3860,62 +3991,65 @@
       <c r="Y57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>28300</v>
+        <v>16100</v>
       </c>
       <c r="E58" s="3">
+        <v>31700</v>
+      </c>
+      <c r="F58" s="3">
         <v>10000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3000</v>
-      </c>
-      <c r="G58" s="3">
-        <v>2900</v>
       </c>
       <c r="H58" s="3">
         <v>2900</v>
       </c>
       <c r="I58" s="3">
+        <v>2900</v>
+      </c>
+      <c r="J58" s="3">
         <v>2600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2200</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L58" s="3">
+      <c r="L58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M58" s="3">
         <v>1200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>700</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3931,62 +4065,65 @@
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>340400</v>
+        <v>411300</v>
       </c>
       <c r="E59" s="3">
-        <v>384400</v>
+        <v>299600</v>
       </c>
       <c r="F59" s="3">
-        <v>394500</v>
+        <v>363300</v>
       </c>
       <c r="G59" s="3">
-        <v>313100</v>
+        <v>349500</v>
       </c>
       <c r="H59" s="3">
-        <v>278300</v>
+        <v>279900</v>
       </c>
       <c r="I59" s="3">
-        <v>362800</v>
+        <v>248400</v>
       </c>
       <c r="J59" s="3">
+        <v>336500</v>
+      </c>
+      <c r="K59" s="3">
         <v>335800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>347600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>312600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>164600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>155300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>84700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>51400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>38600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>43300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>33900</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4002,62 +4139,65 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>368700</v>
+        <v>461300</v>
       </c>
       <c r="E60" s="3">
+        <v>378100</v>
+      </c>
+      <c r="F60" s="3">
         <v>394400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>397500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>316000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>281200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>365400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>338000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>347600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>313900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>166200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>156200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>85600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>52400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>39500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>44000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>34600</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4073,62 +4213,65 @@
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>148800</v>
+        <v>202200</v>
       </c>
       <c r="E61" s="3">
-        <v>73400</v>
+        <v>162700</v>
       </c>
       <c r="F61" s="3">
+        <v>120300</v>
+      </c>
+      <c r="G61" s="3">
         <v>12800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>12700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>14100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>14200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>13900</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
         <v>8800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>900</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -4144,62 +4287,65 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>159200</v>
+        <v>158200</v>
       </c>
       <c r="E62" s="3">
-        <v>88100</v>
+        <v>153700</v>
       </c>
       <c r="F62" s="3">
+        <v>41100</v>
+      </c>
+      <c r="G62" s="3">
         <v>79900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>127500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>146900</v>
       </c>
-      <c r="I62" s="3">
-        <v>125700</v>
-      </c>
       <c r="J62" s="3">
+        <v>125500</v>
+      </c>
+      <c r="K62" s="3">
         <v>110900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>73500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>44500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>261900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>33900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3900</v>
-      </c>
-      <c r="P62" s="3">
-        <v>2900</v>
       </c>
       <c r="Q62" s="3">
         <v>2900</v>
       </c>
       <c r="R62" s="3">
+        <v>2900</v>
+      </c>
+      <c r="S62" s="3">
         <v>3300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4400</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4215,8 +4361,11 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4286,8 +4435,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4357,8 +4509,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4428,62 +4583,65 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>663700</v>
+        <v>824200</v>
       </c>
       <c r="E66" s="3">
-        <v>539300</v>
+        <v>697400</v>
       </c>
       <c r="F66" s="3">
-        <v>469100</v>
+        <v>555800</v>
       </c>
       <c r="G66" s="3">
-        <v>415500</v>
+        <v>490200</v>
       </c>
       <c r="H66" s="3">
-        <v>398300</v>
+        <v>456300</v>
       </c>
       <c r="I66" s="3">
-        <v>460600</v>
+        <v>442200</v>
       </c>
       <c r="J66" s="3">
+        <v>505400</v>
+      </c>
+      <c r="K66" s="3">
         <v>423500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>422300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>367200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>435300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>197000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>90300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>56300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>43200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>49900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>40100</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4499,8 +4657,11 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4526,8 +4687,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4597,8 +4759,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4668,8 +4833,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4739,8 +4907,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4810,62 +4981,65 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
-        <v>-19500</v>
-      </c>
-      <c r="E72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F72" s="3">
         <v>8400</v>
       </c>
-      <c r="F72" s="3">
-        <v>53800</v>
-      </c>
       <c r="G72" s="3">
-        <v>35700</v>
+        <v>50800</v>
       </c>
       <c r="H72" s="3">
-        <v>54200</v>
+        <v>33300</v>
       </c>
       <c r="I72" s="3">
-        <v>51200</v>
+        <v>51900</v>
       </c>
       <c r="J72" s="3">
+        <v>49500</v>
+      </c>
+      <c r="K72" s="3">
         <v>79100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>56200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>70000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>83700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>88700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>94500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>135900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>76300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>62000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>96200</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4881,8 +5055,11 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4952,8 +5129,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5023,8 +5203,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5094,62 +5277,65 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>513200</v>
+        <v>491300</v>
       </c>
       <c r="E76" s="3">
-        <v>505100</v>
+        <v>514800</v>
       </c>
       <c r="F76" s="3">
+        <v>505200</v>
+      </c>
+      <c r="G76" s="3">
         <v>542500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>514200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>551100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>539200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>552800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>514400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>533500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>573400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>564300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>388200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>430100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>370300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>57300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>89900</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5165,8 +5351,11 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5236,73 +5425,76 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5312,68 +5504,71 @@
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>800</v>
+        <v>1500</v>
       </c>
       <c r="E81" s="3">
+        <v>700</v>
+      </c>
+      <c r="F81" s="3">
         <v>15400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>47000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>18500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>35700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>17200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>46600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>12200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>15900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>18300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>13200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>21500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>73400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>14300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>15600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>46600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>18700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>39800</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5383,8 +5578,11 @@
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5410,68 +5608,69 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>3</v>
+      <c r="D83" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E83" s="3">
+        <v>1200</v>
       </c>
       <c r="F83" s="3">
-        <v>7200</v>
+        <v>1100</v>
       </c>
       <c r="G83" s="3">
-        <v>19900</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
+        <v>1100</v>
+      </c>
+      <c r="H83" s="3">
+        <v>1000</v>
       </c>
       <c r="I83" s="3">
-        <v>-15200</v>
+        <v>1000</v>
       </c>
       <c r="J83" s="3">
+        <v>800</v>
+      </c>
+      <c r="K83" s="3">
         <v>21200</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L83" s="3">
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M83" s="3">
         <v>5100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>5200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>8800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>3900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>5800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>2100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>6200</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5481,8 +5680,11 @@
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5552,8 +5754,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5623,8 +5828,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5694,8 +5902,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5765,8 +5976,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5836,8 +6050,11 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -5847,57 +6064,57 @@
       <c r="E89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F89" s="3">
+      <c r="F89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G89" s="3">
         <v>39400</v>
       </c>
-      <c r="G89" s="3">
-        <v>117300</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
+      <c r="H89" s="3">
+        <v>45300</v>
       </c>
       <c r="I89" s="3">
-        <v>-51800</v>
+        <v>42700</v>
       </c>
       <c r="J89" s="3">
+        <v>29300</v>
+      </c>
+      <c r="K89" s="3">
         <v>81100</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L89" s="3">
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M89" s="3">
         <v>7700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>26300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>107600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>47800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>31700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>34600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-6600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>59300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-4200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>48600</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5907,8 +6124,11 @@
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5934,68 +6154,69 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-900</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-400</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G91" s="3">
-        <v>-600</v>
+        <v>-4900</v>
       </c>
       <c r="H91" s="3">
-        <v>-2200</v>
+        <v>-700</v>
       </c>
       <c r="I91" s="3">
-        <v>-3100</v>
-      </c>
-      <c r="J91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K91" s="3">
         <v>-1400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-800</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-200</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-200</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
         <v>-100</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6005,8 +6226,11 @@
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6076,8 +6300,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6147,8 +6374,11 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6158,57 +6388,57 @@
       <c r="E94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F94" s="3">
+      <c r="F94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G94" s="3">
         <v>-8600</v>
       </c>
-      <c r="G94" s="3">
-        <v>70800</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
+      <c r="H94" s="3">
+        <v>2400</v>
       </c>
       <c r="I94" s="3">
-        <v>210600</v>
+        <v>47200</v>
       </c>
       <c r="J94" s="3">
+        <v>21200</v>
+      </c>
+      <c r="K94" s="3">
         <v>-189300</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L94" s="3">
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M94" s="3">
         <v>27900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-230900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-284200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>34800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-283200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-297400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>6500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>17000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-21000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>32300</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6218,8 +6448,11 @@
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6245,56 +6478,57 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>-29400</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G96" s="3">
-        <v>-115700</v>
+        <v>29400</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>37100</v>
       </c>
       <c r="I96" s="3">
-        <v>58000</v>
+        <v>33300</v>
       </c>
       <c r="J96" s="3">
+        <v>45300</v>
+      </c>
+      <c r="K96" s="3">
         <v>-103300</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-29700</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-23600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-119800</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-63000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-37700</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-23300</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
@@ -6316,8 +6550,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6387,8 +6624,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6458,8 +6698,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6529,8 +6772,11 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6540,57 +6786,57 @@
       <c r="E100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F100" s="3">
+      <c r="F100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G100" s="3">
         <v>-32600</v>
       </c>
-      <c r="G100" s="3">
-        <v>-197000</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
+      <c r="H100" s="3">
+        <v>-51600</v>
       </c>
       <c r="I100" s="3">
-        <v>-165700</v>
+        <v>-98200</v>
       </c>
       <c r="J100" s="3">
+        <v>-47200</v>
+      </c>
+      <c r="K100" s="3">
         <v>118500</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L100" s="3">
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3">
         <v>-30500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>201100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>177900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-63500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>262400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>277300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-25600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-40600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-53300</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6600,58 +6846,61 @@
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>3</v>
+      <c r="D101" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-100</v>
       </c>
       <c r="F101" s="3">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
+        <v>1600</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-300</v>
       </c>
       <c r="I101" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="J101" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="N101" s="3">
+        <v>1200</v>
+      </c>
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
         <v>-100</v>
-      </c>
-      <c r="J101" s="3">
-        <v>1000</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="M101" s="3">
-        <v>1200</v>
-      </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
-      <c r="O101" s="3">
-        <v>-100</v>
-      </c>
-      <c r="P101" s="3">
-        <v>200</v>
       </c>
       <c r="Q101" s="3">
         <v>200</v>
       </c>
       <c r="R101" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="S101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="T101" s="3">
         <v>-100</v>
@@ -6659,8 +6908,8 @@
       <c r="U101" s="3">
         <v>-100</v>
       </c>
-      <c r="V101" s="3" t="s">
-        <v>3</v>
+      <c r="V101" s="3">
+        <v>-100</v>
       </c>
       <c r="W101" s="3" t="s">
         <v>3</v>
@@ -6671,68 +6920,71 @@
       <c r="Y101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>3</v>
+      <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
+        <v>0</v>
       </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>-1500</v>
       </c>
-      <c r="G102" s="3">
-        <v>-9000</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>3</v>
+      <c r="H102" s="3">
+        <v>-4800</v>
       </c>
       <c r="I102" s="3">
-        <v>-7000</v>
+        <v>-8400</v>
       </c>
       <c r="J102" s="3">
+        <v>4200</v>
+      </c>
+      <c r="K102" s="3">
         <v>11300</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L102" s="3">
+      <c r="L102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M102" s="3">
         <v>3500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>19100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>11100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>14700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-25600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>35600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-25800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>27600</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6740,6 +6992,9 @@
         <v>3</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PAX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PAX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="92">
   <si>
     <t>PAX</t>
   </si>
@@ -656,103 +656,103 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
@@ -762,71 +762,74 @@
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>78000</v>
+        <v>157300</v>
       </c>
       <c r="E8" s="3">
+        <v>78100</v>
+      </c>
+      <c r="F8" s="3">
         <v>75000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>63900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>111700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>63500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>78600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>73800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>91300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>57000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>55600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>55000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>46200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>39700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>119000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>30600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>31800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>83300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>35200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>88000</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
@@ -836,71 +839,74 @@
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>32900</v>
+        <v>56900</v>
       </c>
       <c r="E9" s="3">
+        <v>32500</v>
+      </c>
+      <c r="F9" s="3">
         <v>32400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>20800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>49400</v>
       </c>
-      <c r="H9" s="3">
-        <v>20200</v>
-      </c>
       <c r="I9" s="3">
+        <v>21700</v>
+      </c>
+      <c r="J9" s="3">
         <v>30400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>29300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>40800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>26000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>27400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>27600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>16400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>15200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>43100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>12000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>7200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>26000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>8700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>34200</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
@@ -910,71 +916,74 @@
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>45100</v>
+        <v>100400</v>
       </c>
       <c r="E10" s="3">
+        <v>45500</v>
+      </c>
+      <c r="F10" s="3">
         <v>42600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>43100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>62300</v>
       </c>
-      <c r="H10" s="3">
-        <v>43300</v>
-      </c>
       <c r="I10" s="3">
+        <v>41800</v>
+      </c>
+      <c r="J10" s="3">
         <v>48200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>44400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>50500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>31000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>28200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>27400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>29800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>24500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>75900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>18600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>24600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>57300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>26500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>53800</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
@@ -984,8 +993,11 @@
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1012,8 +1024,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1086,8 +1099,11 @@
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1160,8 +1176,11 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1169,53 +1188,53 @@
         <v>3</v>
       </c>
       <c r="E14" s="3">
+        <v>19700</v>
+      </c>
+      <c r="F14" s="3">
         <v>20500</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <v>-12800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-2500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>12700</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3">
         <v>5100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>8900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>100</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>2400</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>2200</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1225,8 +1244,8 @@
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
@@ -1234,46 +1253,49 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>6300</v>
+        <v>10800</v>
       </c>
       <c r="E15" s="3">
+        <v>7500</v>
+      </c>
+      <c r="F15" s="3">
         <v>6400</v>
-      </c>
-      <c r="F15" s="3">
-        <v>6100</v>
       </c>
       <c r="G15" s="3">
         <v>6100</v>
       </c>
       <c r="H15" s="3">
+        <v>6100</v>
+      </c>
+      <c r="I15" s="3">
         <v>5900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>5500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>4900</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M15" s="3">
+      <c r="M15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N15" s="3">
         <v>1800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1600</v>
-      </c>
-      <c r="O15" s="3">
-        <v>500</v>
       </c>
       <c r="P15" s="3">
         <v>500</v>
@@ -1285,20 +1307,20 @@
         <v>500</v>
       </c>
       <c r="S15" s="3">
+        <v>500</v>
+      </c>
+      <c r="T15" s="3">
         <v>400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>1300</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>1700</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1308,8 +1330,11 @@
       <c r="Z15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1333,71 +1358,72 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>65200</v>
+        <v>81800</v>
       </c>
       <c r="E17" s="3">
+        <v>52200</v>
+      </c>
+      <c r="F17" s="3">
         <v>50000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>43100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>59100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>39100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>46000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>43200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>44400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>40900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>42100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>37100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>31700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>18300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>46900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>16800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>15100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>34700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>14600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>44000</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1407,71 +1433,74 @@
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>12800</v>
+        <v>75500</v>
       </c>
       <c r="E18" s="3">
+        <v>25900</v>
+      </c>
+      <c r="F18" s="3">
         <v>25000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>20800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>52600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>24500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>32500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>30600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>46900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>16100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>13500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>17900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>14500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>21400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>72100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>13800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>16700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>48600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>20600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>44000</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1481,8 +1510,11 @@
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1509,71 +1541,72 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="F20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G20" s="3">
         <v>200</v>
       </c>
-      <c r="E20" s="3">
-        <v>1000</v>
-      </c>
-      <c r="F20" s="3">
-        <v>200</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>14500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>4200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>6400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-3200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>5200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>400</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>600</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>900</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1583,71 +1616,74 @@
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>18900</v>
+        <v>70400</v>
       </c>
       <c r="E21" s="3">
+        <v>41100</v>
+      </c>
+      <c r="F21" s="3">
         <v>30400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>26700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>44200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>26100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>31600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>38600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>70200</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3">
         <v>21300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>28300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>24100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>22900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>76400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>15800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>18600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>55000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>22700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>51100</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1657,22 +1693,25 @@
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>1400</v>
+        <v>600</v>
       </c>
       <c r="E22" s="3">
+        <v>3800</v>
+      </c>
+      <c r="F22" s="3">
         <v>400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>600</v>
-      </c>
-      <c r="G22" s="3">
-        <v>300</v>
       </c>
       <c r="H22" s="3">
         <v>300</v>
@@ -1683,20 +1722,20 @@
       <c r="J22" s="3">
         <v>300</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
+      <c r="K22" s="3">
+        <v>300</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N22" s="3">
         <v>700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>600</v>
-      </c>
-      <c r="O22" s="3">
-        <v>300</v>
       </c>
       <c r="P22" s="3">
         <v>300</v>
@@ -1708,20 +1747,20 @@
         <v>300</v>
       </c>
       <c r="S22" s="3">
+        <v>300</v>
+      </c>
+      <c r="T22" s="3">
         <v>200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>800</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1731,71 +1770,74 @@
       <c r="Z22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>11200</v>
+        <v>59000</v>
       </c>
       <c r="E23" s="3">
+        <v>10200</v>
+      </c>
+      <c r="F23" s="3">
         <v>3200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>20000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>50700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>18300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>28300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>20700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>49000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>15400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>15600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>22500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>15100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>20700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>72200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>13600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>16500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>48500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>20300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>44100</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1805,71 +1847,74 @@
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E24" s="3">
         <v>8300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>4200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-7700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3100</v>
-      </c>
-      <c r="K24" s="3">
-        <v>2200</v>
       </c>
       <c r="L24" s="3">
         <v>2200</v>
       </c>
       <c r="M24" s="3">
+        <v>2200</v>
+      </c>
+      <c r="N24" s="3">
         <v>-300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>4200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-1200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>3000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>2700</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1879,8 +1924,11 @@
       <c r="Z24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1953,71 +2001,74 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>2900</v>
+        <v>57000</v>
       </c>
       <c r="E26" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F26" s="3">
         <v>2500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>15800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>48400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>18800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>36000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>17600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>46700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>13200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>15900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>18300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>13200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>21500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>73400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>13100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>16300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>45500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>19600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>41400</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2027,71 +2078,74 @@
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1500</v>
+        <v>56800</v>
       </c>
       <c r="E27" s="3">
+        <v>500</v>
+      </c>
+      <c r="F27" s="3">
         <v>700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>15400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>47000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>18500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>35700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>17200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>46600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>12200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>15900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>18300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>13200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>21500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>73400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>14300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>15600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>46600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>18700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>39800</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2101,8 +2155,11 @@
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2175,8 +2232,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2249,8 +2309,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2323,8 +2386,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2397,71 +2463,74 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="E32" s="3">
+        <v>7800</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="G32" s="3">
         <v>-200</v>
       </c>
-      <c r="E32" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-14500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-4200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-6400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>3200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-5200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-400</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-600</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>-900</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2471,71 +2540,74 @@
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1500</v>
+        <v>56800</v>
       </c>
       <c r="E33" s="3">
+        <v>500</v>
+      </c>
+      <c r="F33" s="3">
         <v>700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>15400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>47000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>18500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>35700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>17200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>46600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>12200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>15900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>18300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>13200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>21500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>73400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>14300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>15600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>46600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>18700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>39800</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2545,8 +2617,11 @@
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2619,71 +2694,74 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1500</v>
+        <v>56800</v>
       </c>
       <c r="E35" s="3">
+        <v>500</v>
+      </c>
+      <c r="F35" s="3">
         <v>700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>15400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>47000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>18500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>35700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>17200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>46600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>12200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>15900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>18300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>13200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>21500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>73400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>14300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>15600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>46600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>18700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>39800</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2693,76 +2771,79 @@
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2772,8 +2853,11 @@
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2800,8 +2884,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2828,65 +2913,66 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>33400</v>
+      </c>
+      <c r="E41" s="3">
         <v>38300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>28900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>17300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>16100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>17500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>22400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>30800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>21400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>24400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>13400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>12900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>15300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>44300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>25200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>28700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>14100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>39700</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2902,65 +2988,68 @@
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>62900</v>
+        <v>59000</v>
       </c>
       <c r="E42" s="3">
+        <v>9700</v>
+      </c>
+      <c r="F42" s="3">
         <v>17800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>197600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>17200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>21600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>24900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>10500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>291000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>317000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>328400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>136000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>151900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>250800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>286300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>300400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>9900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>11600</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2976,65 +3065,68 @@
       <c r="Z42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>124000</v>
+        <v>239200</v>
       </c>
       <c r="E43" s="3">
+        <v>131900</v>
+      </c>
+      <c r="F43" s="3">
         <v>126300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>127100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>134600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>118900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>115700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>147600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>137900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>95900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>95600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>105400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>103500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>122300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>113700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>24400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>26000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>10000</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3050,8 +3142,11 @@
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3076,8 +3171,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -3124,65 +3219,68 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>205700</v>
+        <v>56700</v>
       </c>
       <c r="E45" s="3">
+        <v>249800</v>
+      </c>
+      <c r="F45" s="3">
         <v>152700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>104800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>227700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>208000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>210600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>269100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>29300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>51600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>55500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>83900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>81700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1800</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3198,65 +3296,68 @@
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>430900</v>
+        <v>388300</v>
       </c>
       <c r="E46" s="3">
+        <v>437900</v>
+      </c>
+      <c r="F46" s="3">
         <v>333800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>446800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>401600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>372400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>377800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>462300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>479600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>488900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>492900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>338200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>352300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>421400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>428200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>355500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>53700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>63100</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3272,65 +3373,68 @@
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>48900</v>
+      </c>
+      <c r="E47" s="3">
         <v>48400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>49300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>52600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>58600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>54100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>55200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>62700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>50400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>58600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>44100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>282900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>30000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>30600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>31100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>30400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>24500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>36500</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3346,65 +3450,68 @@
       <c r="Z47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>26500</v>
+        <v>32400</v>
       </c>
       <c r="E48" s="3">
+        <v>27500</v>
+      </c>
+      <c r="F48" s="3">
         <v>27700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>28800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>28200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>23800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>25400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>25200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>24600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>24000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>18300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>15800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>13400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3900</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3420,65 +3527,68 @@
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>740300</v>
+        <v>699800</v>
       </c>
       <c r="E49" s="3">
+        <v>750400</v>
+      </c>
+      <c r="F49" s="3">
         <v>712600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>473500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>487000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>438400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>451000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>422600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>411500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>359500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>339800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>366300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>358900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>18300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>19300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>21400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>22400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>23700</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3494,8 +3604,11 @@
       <c r="Z49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3568,8 +3681,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3642,65 +3758,68 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>13400</v>
+      </c>
+      <c r="E52" s="3">
         <v>45500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>25900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>7100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>9000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>9900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>10700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>10000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5700</v>
-      </c>
-      <c r="M52" s="3">
-        <v>5500</v>
       </c>
       <c r="N52" s="3">
         <v>5500</v>
       </c>
       <c r="O52" s="3">
+        <v>5500</v>
+      </c>
+      <c r="P52" s="3">
         <v>6700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2800</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3716,8 +3835,11 @@
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3790,65 +3912,68 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1324400</v>
+        <v>1215000</v>
       </c>
       <c r="E54" s="3">
+        <v>1345500</v>
+      </c>
+      <c r="F54" s="3">
         <v>1182000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1044400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1011600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>929600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>949400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>999800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>976200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>936700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>900700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1008700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>761300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>478500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>486400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>413500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>107200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>130000</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3864,8 +3989,11 @@
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3892,8 +4020,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3920,8 +4049,9 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3929,26 +4059,26 @@
         <v>3</v>
       </c>
       <c r="E57" s="3">
+        <v>26200</v>
+      </c>
+      <c r="F57" s="3">
         <v>12200</v>
       </c>
-      <c r="F57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G57" s="3">
+      <c r="G57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H57" s="3">
         <v>4800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5100</v>
       </c>
-      <c r="K57" s="3">
-        <v>0</v>
-      </c>
       <c r="L57" s="3">
         <v>0</v>
       </c>
@@ -3994,65 +4124,68 @@
       <c r="Z57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>16100</v>
+        <v>78300</v>
       </c>
       <c r="E58" s="3">
+        <v>19500</v>
+      </c>
+      <c r="F58" s="3">
         <v>31700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>10000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3000</v>
-      </c>
-      <c r="H58" s="3">
-        <v>2900</v>
       </c>
       <c r="I58" s="3">
         <v>2900</v>
       </c>
       <c r="J58" s="3">
+        <v>2900</v>
+      </c>
+      <c r="K58" s="3">
         <v>2600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2200</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M58" s="3">
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N58" s="3">
         <v>1200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>700</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4068,65 +4201,68 @@
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>411300</v>
+        <v>258200</v>
       </c>
       <c r="E59" s="3">
+        <v>390900</v>
+      </c>
+      <c r="F59" s="3">
         <v>299600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>363300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>349500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>279900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>248400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>336500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>335800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>347600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>312600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>164600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>155300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>84700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>51400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>38600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>43300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>33900</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4142,65 +4278,68 @@
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>461300</v>
+        <v>403900</v>
       </c>
       <c r="E60" s="3">
+        <v>481700</v>
+      </c>
+      <c r="F60" s="3">
         <v>378100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>394400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>397500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>316000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>281200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>365400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>338000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>347600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>313900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>166200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>156200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>85600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>52400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>39500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>44000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>34600</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4216,65 +4355,68 @@
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>202200</v>
+        <v>149700</v>
       </c>
       <c r="E61" s="3">
+        <v>163600</v>
+      </c>
+      <c r="F61" s="3">
         <v>162700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>120300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>12800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>12700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>14100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>14200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>13900</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
         <v>8800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>7300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>900</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -4290,65 +4432,68 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>158200</v>
+        <v>166000</v>
       </c>
       <c r="E62" s="3">
+        <v>214100</v>
+      </c>
+      <c r="F62" s="3">
         <v>153700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>41100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>79900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>127500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>146900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>125500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>110900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>73500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>44500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>261900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>33900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3900</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>2900</v>
       </c>
       <c r="R62" s="3">
         <v>2900</v>
       </c>
       <c r="S62" s="3">
+        <v>2900</v>
+      </c>
+      <c r="T62" s="3">
         <v>3300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4400</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4364,8 +4509,11 @@
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4438,8 +4586,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4512,8 +4663,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4586,65 +4740,68 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>824200</v>
+        <v>723600</v>
       </c>
       <c r="E66" s="3">
+        <v>861900</v>
+      </c>
+      <c r="F66" s="3">
         <v>697400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>555800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>490200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>456300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>442200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>505400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>423500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>422300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>367200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>435300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>197000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>90300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>56300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>43200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>49900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>40100</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4660,8 +4817,11 @@
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4688,8 +4848,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4762,8 +4923,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4836,8 +5000,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4910,8 +5077,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4984,8 +5154,11 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -4995,54 +5168,54 @@
       <c r="E72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F72" s="3">
+      <c r="F72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G72" s="3">
         <v>8400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>50800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>33300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>51900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>49500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>79100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>56200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>70000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>83700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>88700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>94500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>135900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>76300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>62000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>96200</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5058,8 +5231,11 @@
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5132,8 +5308,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5206,8 +5385,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5280,65 +5462,68 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>491300</v>
+        <v>480600</v>
       </c>
       <c r="E76" s="3">
+        <v>475300</v>
+      </c>
+      <c r="F76" s="3">
         <v>514800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>505200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>542500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>514200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>551100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>539200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>552800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>514400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>533500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>573400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>564300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>388200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>430100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>370300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>57300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>89900</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5354,8 +5539,11 @@
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5428,76 +5616,79 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5507,71 +5698,74 @@
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1500</v>
+        <v>56800</v>
       </c>
       <c r="E81" s="3">
+        <v>500</v>
+      </c>
+      <c r="F81" s="3">
         <v>700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>15400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>47000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>18500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>35700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>17200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>46600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>12200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>15900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>18300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>13200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>21500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>73400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>14300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>15600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>46600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>18700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>39800</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5581,8 +5775,11 @@
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5609,71 +5806,72 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E83" s="3">
         <v>1300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1200</v>
-      </c>
-      <c r="F83" s="3">
-        <v>1100</v>
       </c>
       <c r="G83" s="3">
         <v>1100</v>
       </c>
       <c r="H83" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="I83" s="3">
         <v>1000</v>
       </c>
       <c r="J83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K83" s="3">
         <v>800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>21200</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N83" s="3">
         <v>5100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>5200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>8800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>3900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>2000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>5800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>2100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>6200</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5683,8 +5881,11 @@
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5757,8 +5958,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5831,8 +6035,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5905,8 +6112,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5979,8 +6189,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6053,71 +6266,74 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E89" s="3" t="s">
-        <v>3</v>
+      <c r="E89" s="3">
+        <v>68400</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G89" s="3">
+      <c r="G89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H89" s="3">
         <v>39400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>45300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>42700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>29300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>81100</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M89" s="3">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3">
         <v>7700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>26300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>107600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>47800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>31700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>34600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-6600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>59300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-4200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>48600</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6127,8 +6343,11 @@
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6155,71 +6374,72 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E91" s="3" t="s">
-        <v>3</v>
+      <c r="E91" s="3">
+        <v>-100</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G91" s="3">
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3">
         <v>-4900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-300</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K91" s="3">
+      <c r="K91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L91" s="3">
         <v>-1400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-800</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-200</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-200</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
       <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
         <v>-100</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6229,8 +6449,11 @@
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6303,8 +6526,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6377,71 +6603,74 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E94" s="3" t="s">
-        <v>3</v>
+      <c r="E94" s="3">
+        <v>200</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G94" s="3">
+      <c r="G94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H94" s="3">
         <v>-8600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>2400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>47200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>21200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-189300</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M94" s="3">
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3">
         <v>27900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-230900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-284200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>34800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-283200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-297400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>6500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>17000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-21000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>32300</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6451,8 +6680,11 @@
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6479,59 +6711,60 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E96" s="3" t="s">
-        <v>3</v>
+      <c r="E96" s="3">
+        <v>22900</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G96" s="3">
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3">
         <v>29400</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>37100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>33300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>45300</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-103300</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-29700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-23600</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-119800</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-63000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-37700</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-23300</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
         <v>0</v>
       </c>
@@ -6553,8 +6786,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6627,8 +6863,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6701,8 +6940,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6775,71 +7017,74 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E100" s="3" t="s">
-        <v>3</v>
+      <c r="E100" s="3">
+        <v>-60000</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G100" s="3">
+      <c r="G100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H100" s="3">
         <v>-32600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-51600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-98200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-47200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>118500</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3">
         <v>-30500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>201100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>177900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-63500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>262400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>277300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-25600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-40600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-53300</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6849,61 +7094,64 @@
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1000</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M101" s="3">
+      <c r="M101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N101" s="3">
         <v>-1500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1200</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
       <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-100</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>200</v>
       </c>
       <c r="R101" s="3">
         <v>200</v>
       </c>
       <c r="S101" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="T101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="U101" s="3">
         <v>-100</v>
@@ -6911,8 +7159,8 @@
       <c r="V101" s="3">
         <v>-100</v>
       </c>
-      <c r="W101" s="3" t="s">
-        <v>3</v>
+      <c r="W101" s="3">
+        <v>-100</v>
       </c>
       <c r="X101" s="3" t="s">
         <v>3</v>
@@ -6923,8 +7171,11 @@
       <c r="Z101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -6932,62 +7183,62 @@
         <v>0</v>
       </c>
       <c r="E102" s="3">
-        <v>0</v>
+        <v>9400</v>
       </c>
       <c r="F102" s="3">
         <v>0</v>
       </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>-1500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-4800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-8400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>4200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>11300</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M102" s="3">
+      <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3">
         <v>3500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>19100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>11100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>14700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-25600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>35600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-25800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>27600</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6995,6 +7246,9 @@
         <v>3</v>
       </c>
       <c r="Z102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PAX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PAX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="92">
   <si>
     <t>PAX</t>
   </si>
@@ -656,106 +656,107 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
@@ -765,74 +766,77 @@
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>157300</v>
+        <v>79600</v>
       </c>
       <c r="E8" s="3">
+        <v>157200</v>
+      </c>
+      <c r="F8" s="3">
         <v>78100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>75000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>63900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>111700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>63500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>78600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>73800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>91300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>57000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>55600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>55000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>46200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>39700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>119000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>30600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>31800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>83300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>35200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>88000</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
@@ -842,74 +846,77 @@
       <c r="AA8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>56900</v>
+        <v>27800</v>
       </c>
       <c r="E9" s="3">
+        <v>54800</v>
+      </c>
+      <c r="F9" s="3">
         <v>32500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>32400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>20800</v>
       </c>
-      <c r="H9" s="3">
-        <v>49400</v>
-      </c>
       <c r="I9" s="3">
+        <v>43300</v>
+      </c>
+      <c r="J9" s="3">
         <v>21700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>30400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>29300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>40800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>26000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>27400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>27600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>16400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>15200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>43100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>12000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>7200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>26000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>8700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>34200</v>
       </c>
-      <c r="X9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
@@ -919,74 +926,77 @@
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>100400</v>
+        <v>51800</v>
       </c>
       <c r="E10" s="3">
+        <v>102400</v>
+      </c>
+      <c r="F10" s="3">
         <v>45500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>42600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>43100</v>
       </c>
-      <c r="H10" s="3">
-        <v>62300</v>
-      </c>
       <c r="I10" s="3">
+        <v>68400</v>
+      </c>
+      <c r="J10" s="3">
         <v>41800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>48200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>44400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>50500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>31000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>28200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>27400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>29800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>24500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>75900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>18600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>24600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>57300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>26500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>53800</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
@@ -996,8 +1006,11 @@
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1025,8 +1038,9 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1102,8 +1116,11 @@
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1179,8 +1196,11 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1188,56 +1208,56 @@
         <v>3</v>
       </c>
       <c r="E14" s="3">
+        <v>19500</v>
+      </c>
+      <c r="F14" s="3">
         <v>19700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>20500</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="3">
-        <v>-12800</v>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I14" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="J14" s="3">
         <v>1600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-2500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>12700</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3">
         <v>5100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>8900</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>100</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>2400</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>2200</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1247,8 +1267,8 @@
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1256,49 +1276,52 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E15" s="3">
         <v>10800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>7500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>6400</v>
-      </c>
-      <c r="G15" s="3">
-        <v>6100</v>
       </c>
       <c r="H15" s="3">
         <v>6100</v>
       </c>
       <c r="I15" s="3">
+        <v>6100</v>
+      </c>
+      <c r="J15" s="3">
         <v>5900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>5500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>4900</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N15" s="3">
+      <c r="N15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O15" s="3">
         <v>1800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1600</v>
-      </c>
-      <c r="P15" s="3">
-        <v>500</v>
       </c>
       <c r="Q15" s="3">
         <v>500</v>
@@ -1310,20 +1333,20 @@
         <v>500</v>
       </c>
       <c r="T15" s="3">
+        <v>500</v>
+      </c>
+      <c r="U15" s="3">
         <v>400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>1300</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>1700</v>
       </c>
-      <c r="X15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1333,8 +1356,11 @@
       <c r="AA15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1359,74 +1385,75 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>81800</v>
+        <v>50500</v>
       </c>
       <c r="E17" s="3">
+        <v>79700</v>
+      </c>
+      <c r="F17" s="3">
         <v>52200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>50000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>43100</v>
       </c>
-      <c r="H17" s="3">
-        <v>59100</v>
-      </c>
       <c r="I17" s="3">
+        <v>58000</v>
+      </c>
+      <c r="J17" s="3">
         <v>39100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>46000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>43200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>44400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>40900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>42100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>37100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>31700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>18300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>46900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>16800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>15100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>34700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>14600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>44000</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1436,74 +1463,77 @@
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>75500</v>
+        <v>29100</v>
       </c>
       <c r="E18" s="3">
+        <v>77500</v>
+      </c>
+      <c r="F18" s="3">
         <v>25900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>25000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>20800</v>
       </c>
-      <c r="H18" s="3">
-        <v>52600</v>
-      </c>
       <c r="I18" s="3">
+        <v>53800</v>
+      </c>
+      <c r="J18" s="3">
         <v>24500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>32500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>30600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>46900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>16100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>13500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>17900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>14500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>21400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>72100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>13800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>16700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>48600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>20600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>44000</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1513,8 +1543,11 @@
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1542,74 +1575,75 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>15900</v>
+        <v>100</v>
       </c>
       <c r="E20" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F20" s="3">
         <v>-7800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>200</v>
       </c>
-      <c r="H20" s="3">
-        <v>14500</v>
-      </c>
       <c r="I20" s="3">
+        <v>10500</v>
+      </c>
+      <c r="J20" s="3">
         <v>4200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>6400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-3200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>5200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>400</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>600</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>900</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1619,74 +1653,77 @@
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>70400</v>
+        <v>38000</v>
       </c>
       <c r="E21" s="3">
+        <v>86500</v>
+      </c>
+      <c r="F21" s="3">
         <v>41100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>30400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>26700</v>
       </c>
-      <c r="H21" s="3">
-        <v>44200</v>
-      </c>
       <c r="I21" s="3">
+        <v>49300</v>
+      </c>
+      <c r="J21" s="3">
         <v>26100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>31600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>38600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>70200</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3">
         <v>21300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>28300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>24100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>22900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>76400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>15800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>18600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>55000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>22700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>51100</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1696,25 +1733,28 @@
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E22" s="3">
+        <v>3600</v>
+      </c>
+      <c r="F22" s="3">
+        <v>3800</v>
+      </c>
+      <c r="G22" s="3">
+        <v>400</v>
+      </c>
+      <c r="H22" s="3">
         <v>600</v>
-      </c>
-      <c r="E22" s="3">
-        <v>3800</v>
-      </c>
-      <c r="F22" s="3">
-        <v>400</v>
-      </c>
-      <c r="G22" s="3">
-        <v>600</v>
-      </c>
-      <c r="H22" s="3">
-        <v>300</v>
       </c>
       <c r="I22" s="3">
         <v>300</v>
@@ -1725,20 +1765,20 @@
       <c r="K22" s="3">
         <v>300</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
+      <c r="L22" s="3">
+        <v>300</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N22" s="3">
+      <c r="N22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O22" s="3">
         <v>700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>600</v>
-      </c>
-      <c r="P22" s="3">
-        <v>300</v>
       </c>
       <c r="Q22" s="3">
         <v>300</v>
@@ -1750,20 +1790,20 @@
         <v>300</v>
       </c>
       <c r="T22" s="3">
+        <v>300</v>
+      </c>
+      <c r="U22" s="3">
         <v>200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>800</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1773,74 +1813,77 @@
       <c r="AA22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>59000</v>
+        <v>22000</v>
       </c>
       <c r="E23" s="3">
+        <v>52600</v>
+      </c>
+      <c r="F23" s="3">
         <v>10200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>20000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>50700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>18300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>28300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>20700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>49000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>15400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>15600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>22500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>15100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>20700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>72200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>13600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>16500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>48500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>20300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>44100</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1850,74 +1893,77 @@
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>2000</v>
+        <v>7500</v>
       </c>
       <c r="E24" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="F24" s="3">
         <v>8300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>4200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-7700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3100</v>
-      </c>
-      <c r="L24" s="3">
-        <v>2200</v>
       </c>
       <c r="M24" s="3">
         <v>2200</v>
       </c>
       <c r="N24" s="3">
+        <v>2200</v>
+      </c>
+      <c r="O24" s="3">
         <v>-300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>4200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-1200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>3000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>2700</v>
       </c>
-      <c r="X24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1927,8 +1973,11 @@
       <c r="AA24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2004,74 +2053,77 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>57000</v>
+        <v>14500</v>
       </c>
       <c r="E26" s="3">
+        <v>55400</v>
+      </c>
+      <c r="F26" s="3">
         <v>1900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>15800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>48400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>18800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>36000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>17600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>46700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>13200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>15900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>18300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>13200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>21500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>73400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>13100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>16300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>45500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>19600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>41400</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2081,74 +2133,77 @@
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>56800</v>
+        <v>13600</v>
       </c>
       <c r="E27" s="3">
+        <v>55300</v>
+      </c>
+      <c r="F27" s="3">
         <v>500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>15400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>47000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>18500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>35700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>17200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>46600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>12200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>15900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>18300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>13200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>21500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>73400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>14300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>15600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>46600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>18700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>39800</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2158,8 +2213,11 @@
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2235,8 +2293,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2312,8 +2373,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2389,8 +2453,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2466,74 +2533,77 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-15900</v>
+        <v>-100</v>
       </c>
       <c r="E32" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="F32" s="3">
         <v>7800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-200</v>
       </c>
-      <c r="H32" s="3">
-        <v>-14500</v>
-      </c>
       <c r="I32" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="J32" s="3">
         <v>-4200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-6400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>3200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-5200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-400</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-600</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>-900</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2543,74 +2613,77 @@
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>56800</v>
+        <v>13600</v>
       </c>
       <c r="E33" s="3">
+        <v>55300</v>
+      </c>
+      <c r="F33" s="3">
         <v>500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>15400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>47000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>18500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>35700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>17200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>46600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>12200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>15900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>18300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>13200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>21500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>73400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>14300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>15600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>46600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>18700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>39800</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2620,8 +2693,11 @@
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2697,74 +2773,77 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>56800</v>
+        <v>13600</v>
       </c>
       <c r="E35" s="3">
+        <v>55300</v>
+      </c>
+      <c r="F35" s="3">
         <v>500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>15400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>47000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>18500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>35700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>17200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>46600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>12200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>15900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>18300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>13200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>21500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>73400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>14300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>15600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>46600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>18700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>39800</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2774,79 +2853,82 @@
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2856,8 +2938,11 @@
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2885,8 +2970,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2914,68 +3000,69 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>34500</v>
+      </c>
+      <c r="E41" s="3">
         <v>33400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>38300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>28900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>17300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>16100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>17500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>22400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>30800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>21400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>24400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>13400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>12900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>15300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>44300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>25200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>28700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>14100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>39700</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2991,68 +3078,71 @@
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>59000</v>
+        <v>69300</v>
       </c>
       <c r="E42" s="3">
+        <v>5000</v>
+      </c>
+      <c r="F42" s="3">
         <v>9700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>17800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>197600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>17200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>21600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>24900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>10500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>291000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>317000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>328400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>136000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>151900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>250800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>286300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>300400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>9900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>11600</v>
       </c>
-      <c r="V42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3068,68 +3158,71 @@
       <c r="AA42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>239200</v>
+        <v>156200</v>
       </c>
       <c r="E43" s="3">
+        <v>227100</v>
+      </c>
+      <c r="F43" s="3">
         <v>131900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>126300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>127100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>134600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>118900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>115700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>147600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>137900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>95900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>95600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>105400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>103500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>122300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>113700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>24400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>26000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>10000</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3145,8 +3238,11 @@
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3174,8 +3270,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3222,68 +3318,71 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>56700</v>
+        <v>122700</v>
       </c>
       <c r="E45" s="3">
+        <v>100100</v>
+      </c>
+      <c r="F45" s="3">
         <v>249800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>152700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>104800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>227700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>208000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>210600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>269100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>29300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>51600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>55500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>83900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>81700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1800</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3299,68 +3398,71 @@
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>388300</v>
+        <v>382700</v>
       </c>
       <c r="E46" s="3">
+        <v>372700</v>
+      </c>
+      <c r="F46" s="3">
         <v>437900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>333800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>446800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>401600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>372400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>377800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>462300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>479600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>488900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>492900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>338200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>352300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>421400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>428200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>355500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>53700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>63100</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3376,68 +3478,71 @@
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>48900</v>
+        <v>67100</v>
       </c>
       <c r="E47" s="3">
+        <v>50000</v>
+      </c>
+      <c r="F47" s="3">
         <v>48400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>49300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>52600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>58600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>54100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>55200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>62700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>50400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>58600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>44100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>282900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>30000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>30600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>31100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>30400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>24500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>36500</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3453,68 +3558,71 @@
       <c r="AA47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>32400</v>
+        <v>34900</v>
       </c>
       <c r="E48" s="3">
+        <v>32600</v>
+      </c>
+      <c r="F48" s="3">
         <v>27500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>27700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>28800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>28200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>23800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>25400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>25200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>24600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>24000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>18300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>15800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>13400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>4100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3900</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3530,68 +3638,71 @@
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>699800</v>
+        <v>725500</v>
       </c>
       <c r="E49" s="3">
+        <v>700900</v>
+      </c>
+      <c r="F49" s="3">
         <v>750400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>712600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>473500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>487000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>438400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>451000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>422600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>411500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>359500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>339800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>366300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>358900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>18300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>19300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>21400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>22400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>23700</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3607,8 +3718,11 @@
       <c r="AA49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3684,8 +3798,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3761,68 +3878,71 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>13400</v>
+        <v>35200</v>
       </c>
       <c r="E52" s="3">
+        <v>14100</v>
+      </c>
+      <c r="F52" s="3">
         <v>45500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>25900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>7100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>9000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>9900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>10700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>10000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5700</v>
-      </c>
-      <c r="N52" s="3">
-        <v>5500</v>
       </c>
       <c r="O52" s="3">
         <v>5500</v>
       </c>
       <c r="P52" s="3">
+        <v>5500</v>
+      </c>
+      <c r="Q52" s="3">
         <v>6700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2800</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3838,8 +3958,11 @@
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3915,68 +4038,71 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1215000</v>
+        <v>1279100</v>
       </c>
       <c r="E54" s="3">
+        <v>1206100</v>
+      </c>
+      <c r="F54" s="3">
         <v>1345500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1182000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1044400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1011600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>929600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>949400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>999800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>976200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>936700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>900700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1008700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>761300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>478500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>486400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>413500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>107200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>130000</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3992,8 +4118,11 @@
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4021,8 +4150,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4050,8 +4180,9 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4059,29 +4190,29 @@
         <v>3</v>
       </c>
       <c r="E57" s="3">
+        <v>41800</v>
+      </c>
+      <c r="F57" s="3">
         <v>26200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>12200</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="H57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I57" s="3">
         <v>4800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5100</v>
       </c>
-      <c r="L57" s="3">
-        <v>0</v>
-      </c>
       <c r="M57" s="3">
         <v>0</v>
       </c>
@@ -4127,68 +4258,71 @@
       <c r="AA57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>78300</v>
+        <v>41100</v>
       </c>
       <c r="E58" s="3">
+        <v>82200</v>
+      </c>
+      <c r="F58" s="3">
         <v>19500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>31700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>10000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3000</v>
-      </c>
-      <c r="I58" s="3">
-        <v>2900</v>
       </c>
       <c r="J58" s="3">
         <v>2900</v>
       </c>
       <c r="K58" s="3">
+        <v>2900</v>
+      </c>
+      <c r="L58" s="3">
         <v>2600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2200</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N58" s="3">
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O58" s="3">
         <v>1200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>700</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4204,68 +4338,71 @@
       <c r="AA58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>258200</v>
+        <v>303500</v>
       </c>
       <c r="E59" s="3">
+        <v>201400</v>
+      </c>
+      <c r="F59" s="3">
         <v>390900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>299600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>363300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>349500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>279900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>248400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>336500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>335800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>347600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>312600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>164600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>155300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>84700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>51400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>38600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>43300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>33900</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4281,68 +4418,71 @@
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>403900</v>
+        <v>395300</v>
       </c>
       <c r="E60" s="3">
+        <v>397400</v>
+      </c>
+      <c r="F60" s="3">
         <v>481700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>378100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>394400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>397500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>316000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>281200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>365400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>338000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>347600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>313900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>166200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>156200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>85600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>52400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>39500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>44000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>34600</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4358,68 +4498,71 @@
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>149700</v>
+        <v>151000</v>
       </c>
       <c r="E61" s="3">
+        <v>168200</v>
+      </c>
+      <c r="F61" s="3">
         <v>163600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>162700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>120300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>12800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>12700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>14100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>14200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>13900</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>8800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>7300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>6900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>900</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
@@ -4435,68 +4578,71 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>166000</v>
+        <v>169100</v>
       </c>
       <c r="E62" s="3">
+        <v>147800</v>
+      </c>
+      <c r="F62" s="3">
         <v>214100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>153700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>41100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>79900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>127500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>146900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>125500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>110900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>73500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>44500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>261900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>33900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3900</v>
-      </c>
-      <c r="R62" s="3">
-        <v>2900</v>
       </c>
       <c r="S62" s="3">
         <v>2900</v>
       </c>
       <c r="T62" s="3">
+        <v>2900</v>
+      </c>
+      <c r="U62" s="3">
         <v>3300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4400</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4512,8 +4658,11 @@
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4589,8 +4738,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4666,8 +4818,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4743,68 +4898,71 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>723600</v>
+        <v>718100</v>
       </c>
       <c r="E66" s="3">
+        <v>715200</v>
+      </c>
+      <c r="F66" s="3">
         <v>861900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>697400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>555800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>490200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>456300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>442200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>505400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>423500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>422300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>367200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>435300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>197000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>90300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>56300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>43200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>49900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>40100</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4820,8 +4978,11 @@
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4849,8 +5010,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4926,8 +5088,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5003,8 +5168,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5080,8 +5248,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5157,8 +5328,11 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -5171,54 +5345,54 @@
       <c r="F72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G72" s="3">
+      <c r="G72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H72" s="3">
         <v>8400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>50800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>33300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>51900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>49500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>79100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>56200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>70000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>83700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>88700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>94500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>135900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>76300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>62000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>96200</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5234,8 +5408,11 @@
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5311,8 +5488,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5388,8 +5568,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5465,68 +5648,71 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>480600</v>
+        <v>549400</v>
       </c>
       <c r="E76" s="3">
+        <v>481100</v>
+      </c>
+      <c r="F76" s="3">
         <v>475300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>514800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>505200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>542500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>514200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>551100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>539200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>552800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>514400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>533500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>573400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>564300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>388200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>430100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>370300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>57300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>89900</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5542,8 +5728,11 @@
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5619,79 +5808,82 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5701,74 +5893,77 @@
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>56800</v>
+        <v>13600</v>
       </c>
       <c r="E81" s="3">
+        <v>55300</v>
+      </c>
+      <c r="F81" s="3">
         <v>500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>15400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>47000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>18500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>35700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>17200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>46600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>12200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>15900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>18300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>13200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>21500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>73400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>14300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>15600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>46600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>18700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>39800</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5778,8 +5973,11 @@
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5807,74 +6005,75 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E83" s="3">
         <v>1100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1200</v>
-      </c>
-      <c r="G83" s="3">
-        <v>1100</v>
       </c>
       <c r="H83" s="3">
         <v>1100</v>
       </c>
       <c r="I83" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="J83" s="3">
         <v>1000</v>
       </c>
       <c r="K83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L83" s="3">
         <v>800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>21200</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N83" s="3">
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3">
         <v>5100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>5200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>8800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>3900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>2000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>5800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>2100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>6200</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5884,8 +6083,11 @@
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5961,8 +6163,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6038,8 +6243,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6115,8 +6323,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6192,8 +6403,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6269,8 +6483,11 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -6278,65 +6495,65 @@
         <v>3</v>
       </c>
       <c r="E89" s="3">
+        <v>25900</v>
+      </c>
+      <c r="F89" s="3">
         <v>68400</v>
       </c>
-      <c r="F89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H89" s="3">
+      <c r="H89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I89" s="3">
         <v>39400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>45300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>42700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>29300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>81100</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N89" s="3">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3">
         <v>7700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>26300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>107600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>47800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>31700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>34600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-6600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>59300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-4200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>48600</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6346,8 +6563,11 @@
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6375,8 +6595,9 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6384,65 +6605,65 @@
         <v>3</v>
       </c>
       <c r="E91" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H91" s="3">
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3">
         <v>-4900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-300</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L91" s="3">
+      <c r="L91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M91" s="3">
         <v>-1400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-800</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-200</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
         <v>-200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-200</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
       <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
         <v>-100</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6452,8 +6673,11 @@
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6529,8 +6753,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6606,8 +6833,11 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6615,65 +6845,65 @@
         <v>3</v>
       </c>
       <c r="E94" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F94" s="3">
         <v>200</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H94" s="3">
+      <c r="H94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I94" s="3">
         <v>-8600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>2400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>47200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>21200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-189300</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3">
         <v>27900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-230900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-284200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>34800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-283200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-297400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>6500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>17000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-21000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>32300</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6683,8 +6913,11 @@
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6712,8 +6945,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6721,53 +6955,53 @@
         <v>3</v>
       </c>
       <c r="E96" s="3">
+        <v>23000</v>
+      </c>
+      <c r="F96" s="3">
         <v>22900</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H96" s="3">
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3">
         <v>29400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>37100</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>33300</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>45300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-103300</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-29700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-23600</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-119800</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-63000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-37700</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-23300</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
         <v>0</v>
       </c>
@@ -6789,8 +7023,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6866,8 +7103,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6943,8 +7183,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7020,8 +7263,11 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7029,65 +7275,65 @@
         <v>3</v>
       </c>
       <c r="E100" s="3">
+        <v>-31100</v>
+      </c>
+      <c r="F100" s="3">
         <v>-60000</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H100" s="3">
+      <c r="H100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I100" s="3">
         <v>-32600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-51600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-98200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-47200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>118500</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3">
         <v>-30500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>201100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>177900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-63500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>262400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>277300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-25600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-40600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-53300</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7097,64 +7343,67 @@
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3">
         <v>300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1000</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N101" s="3">
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O101" s="3">
         <v>-1500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1200</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
       <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
         <v>-100</v>
-      </c>
-      <c r="R101" s="3">
-        <v>200</v>
       </c>
       <c r="S101" s="3">
         <v>200</v>
       </c>
       <c r="T101" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="U101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V101" s="3">
         <v>-100</v>
@@ -7162,8 +7411,8 @@
       <c r="W101" s="3">
         <v>-100</v>
       </c>
-      <c r="X101" s="3" t="s">
-        <v>3</v>
+      <c r="X101" s="3">
+        <v>-100</v>
       </c>
       <c r="Y101" s="3" t="s">
         <v>3</v>
@@ -7174,8 +7423,11 @@
       <c r="AA101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -7183,65 +7435,65 @@
         <v>0</v>
       </c>
       <c r="E102" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="F102" s="3">
         <v>9400</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
       <c r="G102" s="3">
         <v>0</v>
       </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>-1500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-4800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-8400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>4200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>11300</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N102" s="3">
+      <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3">
         <v>3500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>19100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>11100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>14700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-25600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>35600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-25800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>27600</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7249,6 +7501,9 @@
         <v>3</v>
       </c>
       <c r="AA102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PAX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PAX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="92">
   <si>
     <t>PAX</t>
   </si>
@@ -656,110 +656,111 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
@@ -769,77 +770,80 @@
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3">
         <v>79600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>157200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>78100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>75000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>63900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>111700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>63500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>78600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>73800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>91300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>57000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>55600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>55000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>46200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>39700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>119000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>30600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>31800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>83300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>35200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>88000</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
@@ -849,77 +853,80 @@
       <c r="AB8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3">
-        <v>27800</v>
+      <c r="D9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E9" s="3">
+        <v>28700</v>
+      </c>
+      <c r="F9" s="3">
         <v>54800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>32500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>32400</v>
       </c>
-      <c r="H9" s="3">
-        <v>20800</v>
-      </c>
       <c r="I9" s="3">
+        <v>20300</v>
+      </c>
+      <c r="J9" s="3">
         <v>43300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>21700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>30400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>29300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>40800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>26000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>27400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>27600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>16400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>15200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>43100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>12000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>7200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>26000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>8700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>34200</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
@@ -929,77 +936,80 @@
       <c r="AB9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
-        <v>51800</v>
+      <c r="D10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E10" s="3">
+        <v>50900</v>
+      </c>
+      <c r="F10" s="3">
         <v>102400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>45500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>42600</v>
       </c>
-      <c r="H10" s="3">
-        <v>43100</v>
-      </c>
       <c r="I10" s="3">
+        <v>43600</v>
+      </c>
+      <c r="J10" s="3">
         <v>68400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>41800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>48200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>44400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>50500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>31000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>28200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>27400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>29800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>24500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>75900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>18600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>24600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>57300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>26500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>53800</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1009,8 +1019,11 @@
       <c r="AB10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1039,8 +1052,9 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1119,8 +1133,11 @@
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1199,8 +1216,11 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1208,59 +1228,59 @@
         <v>3</v>
       </c>
       <c r="E14" s="3">
+        <v>5100</v>
+      </c>
+      <c r="F14" s="3">
         <v>19500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>19700</v>
       </c>
-      <c r="G14" s="3">
-        <v>20500</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
+      <c r="H14" s="3">
+        <v>17500</v>
       </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>-7700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-2500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>12700</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3">
         <v>5100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1800</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>8900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>100</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>2400</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>2200</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1270,8 +1290,8 @@
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1279,52 +1299,55 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="E15" s="3">
+        <v>9900</v>
+      </c>
+      <c r="F15" s="3">
         <v>10800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>7500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>6400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
+        <v>6000</v>
+      </c>
+      <c r="J15" s="3">
         <v>6100</v>
       </c>
-      <c r="I15" s="3">
-        <v>6100</v>
-      </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>5900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>5500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>4900</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O15" s="3">
+      <c r="O15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P15" s="3">
         <v>1800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1600</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>500</v>
       </c>
       <c r="R15" s="3">
         <v>500</v>
@@ -1336,20 +1359,20 @@
         <v>500</v>
       </c>
       <c r="U15" s="3">
+        <v>500</v>
+      </c>
+      <c r="V15" s="3">
         <v>400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>1300</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>500</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>1700</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1359,8 +1382,11 @@
       <c r="AB15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1386,77 +1412,78 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>50500</v>
+      <c r="D17" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E17" s="3">
+        <v>50600</v>
+      </c>
+      <c r="F17" s="3">
         <v>79700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>52200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>50000</v>
       </c>
-      <c r="H17" s="3">
-        <v>43100</v>
-      </c>
       <c r="I17" s="3">
+        <v>35500</v>
+      </c>
+      <c r="J17" s="3">
         <v>58000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>39100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>46000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>43200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>44400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>40900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>42100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>37100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>31700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>18300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>46900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>16800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>15100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>34700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>14600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>44000</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1466,77 +1493,80 @@
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>29100</v>
+      <c r="D18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>28900</v>
+      </c>
+      <c r="F18" s="3">
         <v>77500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>25900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>25000</v>
       </c>
-      <c r="H18" s="3">
-        <v>20800</v>
-      </c>
       <c r="I18" s="3">
+        <v>28400</v>
+      </c>
+      <c r="J18" s="3">
         <v>53800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>24500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>32500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>30600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>46900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>16100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>13500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>17900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>14500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>21400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>72100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>13800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>16700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>48600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>20600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>44000</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1546,8 +1576,11 @@
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1576,77 +1609,78 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>100</v>
+      <c r="D20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>5300</v>
+      </c>
+      <c r="F20" s="3">
         <v>1900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-7800</v>
       </c>
-      <c r="G20" s="3">
-        <v>1000</v>
-      </c>
       <c r="H20" s="3">
-        <v>200</v>
+        <v>1100</v>
       </c>
       <c r="I20" s="3">
+        <v>8000</v>
+      </c>
+      <c r="J20" s="3">
         <v>10500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>4200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>6400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-3200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>2700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>5200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>400</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
         <v>0</v>
       </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>600</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>900</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1656,77 +1690,80 @@
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>38000</v>
+        <v>0</v>
       </c>
       <c r="E21" s="3">
+        <v>33500</v>
+      </c>
+      <c r="F21" s="3">
         <v>86500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>41100</v>
       </c>
-      <c r="G21" s="3">
-        <v>30400</v>
-      </c>
       <c r="H21" s="3">
-        <v>26700</v>
+        <v>30300</v>
       </c>
       <c r="I21" s="3">
+        <v>26400</v>
+      </c>
+      <c r="J21" s="3">
         <v>49300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>26100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>31600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>38600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>70200</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3">
         <v>21300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>28300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>24100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>22900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>76400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>15800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>18600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>55000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>22700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>51100</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1736,25 +1773,28 @@
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>7000</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E22" s="3">
+        <v>3900</v>
+      </c>
+      <c r="F22" s="3">
         <v>3600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>3800</v>
       </c>
-      <c r="G22" s="3">
-        <v>400</v>
-      </c>
       <c r="H22" s="3">
-        <v>600</v>
+        <v>3300</v>
       </c>
       <c r="I22" s="3">
         <v>300</v>
@@ -1768,20 +1808,20 @@
       <c r="L22" s="3">
         <v>300</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
+      <c r="M22" s="3">
+        <v>300</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" s="3">
         <v>700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>600</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>300</v>
       </c>
       <c r="R22" s="3">
         <v>300</v>
@@ -1793,20 +1833,20 @@
         <v>300</v>
       </c>
       <c r="U22" s="3">
+        <v>300</v>
+      </c>
+      <c r="V22" s="3">
         <v>200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>800</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1816,77 +1856,80 @@
       <c r="AB22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>22000</v>
+      <c r="D23" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E23" s="3">
+        <v>14600</v>
+      </c>
+      <c r="F23" s="3">
         <v>52600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>10200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3200</v>
       </c>
-      <c r="H23" s="3">
-        <v>20000</v>
-      </c>
       <c r="I23" s="3">
+        <v>20100</v>
+      </c>
+      <c r="J23" s="3">
         <v>50700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>18300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>28300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>20700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>49000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>15400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>15600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>22500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>15100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>20700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>72200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>13600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>16500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>48500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>20300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>44100</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1896,77 +1939,80 @@
       <c r="AB23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>7500</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E24" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F24" s="3">
         <v>-2800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>8300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-7700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3100</v>
-      </c>
-      <c r="M24" s="3">
-        <v>2200</v>
       </c>
       <c r="N24" s="3">
         <v>2200</v>
       </c>
       <c r="O24" s="3">
+        <v>2200</v>
+      </c>
+      <c r="P24" s="3">
         <v>-300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>4200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-1200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>3000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>2700</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1976,8 +2022,11 @@
       <c r="AB24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2056,77 +2105,80 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>14500</v>
+      <c r="D26" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E26" s="3">
+        <v>16600</v>
+      </c>
+      <c r="F26" s="3">
         <v>55400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2500</v>
       </c>
-      <c r="H26" s="3">
-        <v>15800</v>
-      </c>
       <c r="I26" s="3">
+        <v>15900</v>
+      </c>
+      <c r="J26" s="3">
         <v>48400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>18800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>36000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>17600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>46700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>13200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>15900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>18300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>13200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>21500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>73400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>13100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>16300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>45500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>19600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>41400</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2136,77 +2188,80 @@
       <c r="AB26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>13600</v>
+      <c r="D27" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E27" s="3">
+        <v>15700</v>
+      </c>
+      <c r="F27" s="3">
         <v>55300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>15400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>47000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>18500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>35700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>17200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>46600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>12200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>15900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>18300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>13200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>21500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>73400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>14300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>15600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>46600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>18700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>39800</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2216,8 +2271,11 @@
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2296,8 +2354,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2376,8 +2437,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2456,8 +2520,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2536,77 +2603,80 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-100</v>
+      <c r="D32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="F32" s="3">
         <v>-1900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>7800</v>
       </c>
-      <c r="G32" s="3">
-        <v>-1000</v>
-      </c>
       <c r="H32" s="3">
-        <v>-200</v>
+        <v>-1100</v>
       </c>
       <c r="I32" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="J32" s="3">
         <v>-10500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-4200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-6400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>3200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-2700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-400</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
         <v>0</v>
       </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>-600</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-900</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2616,77 +2686,80 @@
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>13600</v>
+      <c r="D33" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E33" s="3">
+        <v>15700</v>
+      </c>
+      <c r="F33" s="3">
         <v>55300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>15400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>47000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>18500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>35700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>17200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>46600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>12200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>15900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>18300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>13200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>21500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>73400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>14300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>15600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>46600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>18700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>39800</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2696,8 +2769,11 @@
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2776,77 +2852,80 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>13600</v>
+      <c r="D35" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E35" s="3">
+        <v>15700</v>
+      </c>
+      <c r="F35" s="3">
         <v>55300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>15400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>47000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>18500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>35700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>17200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>46600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>12200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>15900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>18300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>13200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>21500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>73400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>14300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>15600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>46600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>18700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>39800</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2856,82 +2935,85 @@
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2941,8 +3023,11 @@
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2971,8 +3056,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3001,71 +3087,72 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
-        <v>34500</v>
+      <c r="D41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E41" s="3">
+        <v>36100</v>
+      </c>
+      <c r="F41" s="3">
         <v>33400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>38300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>28900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>17300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>16100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>17500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>22400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>30800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>21400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>24400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>13400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>12900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>15300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>44300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>25200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>28700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>14100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>39700</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3081,71 +3168,74 @@
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>69300</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>14600</v>
+      </c>
+      <c r="F42" s="3">
         <v>5000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>9700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>17800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>197600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>17200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>21600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>24900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>10500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>291000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>317000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>328400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>136000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>151900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>250800</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>286300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>300400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>9900</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>11600</v>
       </c>
-      <c r="W42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3161,71 +3251,74 @@
       <c r="AB42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>156200</v>
+      <c r="D43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E43" s="3">
+        <v>172100</v>
+      </c>
+      <c r="F43" s="3">
         <v>227100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>131900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>126300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>127100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>134600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>118900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>115700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>147600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>137900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>95900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>95600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>105400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>103500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>122300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>113700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>24400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>26000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>10000</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3241,8 +3334,11 @@
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3273,8 +3369,8 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -3321,71 +3417,74 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>122700</v>
+      <c r="D45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E45" s="3">
+        <v>166100</v>
+      </c>
+      <c r="F45" s="3">
         <v>100100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>249800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>152700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>104800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>227700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>208000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>210600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>269100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>29300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>51600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>55500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>83900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>81700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>4000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1800</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3401,71 +3500,74 @@
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
-        <v>382700</v>
+      <c r="D46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E46" s="3">
+        <v>397200</v>
+      </c>
+      <c r="F46" s="3">
         <v>372700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>437900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>333800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>446800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>401600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>372400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>377800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>462300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>479600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>488900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>492900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>338200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>352300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>421400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>428200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>355500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>53700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>63100</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3481,71 +3583,74 @@
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>67100</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E47" s="3">
+        <v>59900</v>
+      </c>
+      <c r="F47" s="3">
         <v>50000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>48400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>49300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>52600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>58600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>54100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>55200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>62700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>50400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>58600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>44100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>282900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>30000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>30600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>31100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>30400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>24500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>36500</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3561,71 +3666,74 @@
       <c r="AB47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E48" s="3">
         <v>34900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>32600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>27500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>27700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>28800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>28200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>23800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>25400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>25200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>24600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>24000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>18300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>15800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>13400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>4000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>4100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3900</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3641,71 +3749,74 @@
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
-        <v>725500</v>
+      <c r="D49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E49" s="3">
+        <v>777100</v>
+      </c>
+      <c r="F49" s="3">
         <v>700900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>750400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>712600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>473500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>487000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>438400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>451000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>422600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>411500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>359500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>339800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>366300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>358900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>18300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>19300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>21400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>22400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>23700</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3721,8 +3832,11 @@
       <c r="AB49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3801,8 +3915,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3881,71 +3998,74 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>35200</v>
+      <c r="D52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E52" s="3">
+        <v>27700</v>
+      </c>
+      <c r="F52" s="3">
         <v>14100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>45500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>25900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>9000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>9900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>10700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>10000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5700</v>
-      </c>
-      <c r="O52" s="3">
-        <v>5500</v>
       </c>
       <c r="P52" s="3">
         <v>5500</v>
       </c>
       <c r="Q52" s="3">
+        <v>5500</v>
+      </c>
+      <c r="R52" s="3">
         <v>6700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2800</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3961,8 +4081,11 @@
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4041,71 +4164,74 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
-        <v>1279100</v>
+      <c r="D54" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E54" s="3">
+        <v>1334000</v>
+      </c>
+      <c r="F54" s="3">
         <v>1206100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1345500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1182000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1044400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1011600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>929600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>949400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>999800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>976200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>936700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>900700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1008700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>761300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>478500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>486400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>413500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>107200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>130000</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4121,8 +4247,11 @@
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4151,8 +4280,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4181,8 +4311,9 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4190,32 +4321,32 @@
         <v>3</v>
       </c>
       <c r="E57" s="3">
+        <v>66300</v>
+      </c>
+      <c r="F57" s="3">
         <v>41800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>26200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>12200</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I57" s="3">
+      <c r="I57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J57" s="3">
         <v>4800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5100</v>
       </c>
-      <c r="M57" s="3">
-        <v>0</v>
-      </c>
       <c r="N57" s="3">
         <v>0</v>
       </c>
@@ -4261,71 +4392,74 @@
       <c r="AB57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
-        <v>41100</v>
+      <c r="D58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E58" s="3">
+        <v>45900</v>
+      </c>
+      <c r="F58" s="3">
         <v>82200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>19500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>31700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>10000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3000</v>
-      </c>
-      <c r="J58" s="3">
-        <v>2900</v>
       </c>
       <c r="K58" s="3">
         <v>2900</v>
       </c>
       <c r="L58" s="3">
+        <v>2900</v>
+      </c>
+      <c r="M58" s="3">
         <v>2600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2200</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O58" s="3">
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P58" s="3">
         <v>1200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>700</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4341,71 +4475,74 @@
       <c r="AB58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>303500</v>
+      <c r="D59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E59" s="3">
+        <v>245200</v>
+      </c>
+      <c r="F59" s="3">
         <v>201400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>390900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>299600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>363300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>349500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>279900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>248400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>336500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>335800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>347600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>312600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>164600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>155300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>84700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>51400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>38600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>43300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>33900</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4421,71 +4558,74 @@
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
-        <v>395300</v>
+      <c r="D60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E60" s="3">
+        <v>410800</v>
+      </c>
+      <c r="F60" s="3">
         <v>397400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>481700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>378100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>394400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>397500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>316000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>281200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>365400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>338000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>347600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>313900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>166200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>156200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>85600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>52400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>39500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>44000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>34600</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4501,71 +4641,74 @@
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>151000</v>
+        <v>0</v>
       </c>
       <c r="E61" s="3">
+        <v>169000</v>
+      </c>
+      <c r="F61" s="3">
         <v>168200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>163600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>162700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>120300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>12800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>12700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>14100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>14200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>13900</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>8800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>7300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>6900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>900</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -4581,71 +4724,74 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>169100</v>
+      <c r="D62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E62" s="3">
+        <v>148200</v>
+      </c>
+      <c r="F62" s="3">
         <v>147800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>214100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>153700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>41100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>79900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>127500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>146900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>125500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>110900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>73500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>44500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>261900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>33900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3900</v>
-      </c>
-      <c r="S62" s="3">
-        <v>2900</v>
       </c>
       <c r="T62" s="3">
         <v>2900</v>
       </c>
       <c r="U62" s="3">
+        <v>2900</v>
+      </c>
+      <c r="V62" s="3">
         <v>3300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4400</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4661,8 +4807,11 @@
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4741,8 +4890,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4821,8 +4973,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4901,71 +5056,74 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
-        <v>718100</v>
+      <c r="D66" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E66" s="3">
+        <v>777800</v>
+      </c>
+      <c r="F66" s="3">
         <v>715200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>861900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>697400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>555800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>490200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>456300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>442200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>505400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>423500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>422300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>367200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>435300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>197000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>90300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>56300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>43200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>49900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>40100</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4981,8 +5139,11 @@
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5011,8 +5172,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5091,8 +5253,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5171,8 +5336,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5251,8 +5419,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5331,8 +5502,11 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -5348,54 +5522,54 @@
       <c r="G72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H72" s="3">
+      <c r="H72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I72" s="3">
         <v>8400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>50800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>33300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>51900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>49500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>79100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>56200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>70000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>83700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>88700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>94500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>135900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>76300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>62000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>96200</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5411,8 +5585,11 @@
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5491,8 +5668,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5571,8 +5751,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5651,71 +5834,74 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
-        <v>549400</v>
+      <c r="D76" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E76" s="3">
+        <v>545500</v>
+      </c>
+      <c r="F76" s="3">
         <v>481100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>475300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>514800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>505200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>542500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>514200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>551100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>539200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>552800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>514400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>533500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>573400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>564300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>388200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>430100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>370300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>57300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>89900</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5731,8 +5917,11 @@
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5811,82 +6000,85 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5896,77 +6088,80 @@
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>13600</v>
+      <c r="D81" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E81" s="3">
+        <v>15700</v>
+      </c>
+      <c r="F81" s="3">
         <v>55300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>15400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>47000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>18500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>35700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>17200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>46600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>12200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>15900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>18300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>13200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>21500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>73400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>14300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>15600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>46600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>18700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>39800</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5976,8 +6171,11 @@
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6006,8 +6204,9 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6015,68 +6214,68 @@
         <v>3</v>
       </c>
       <c r="E83" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F83" s="3">
         <v>1100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1200</v>
-      </c>
-      <c r="H83" s="3">
-        <v>1100</v>
       </c>
       <c r="I83" s="3">
         <v>1100</v>
       </c>
       <c r="J83" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="K83" s="3">
         <v>1000</v>
       </c>
       <c r="L83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="M83" s="3">
         <v>800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>21200</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P83" s="3">
         <v>5100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>5200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>8800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>3900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>2000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>5800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>2100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>6200</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6086,8 +6285,11 @@
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6166,8 +6368,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6246,8 +6451,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6326,8 +6534,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6406,8 +6617,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6486,8 +6700,11 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -6495,68 +6712,68 @@
         <v>3</v>
       </c>
       <c r="E89" s="3">
+        <v>100100</v>
+      </c>
+      <c r="F89" s="3">
         <v>25900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>68400</v>
       </c>
-      <c r="G89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I89" s="3">
+        <v>41900</v>
+      </c>
+      <c r="J89" s="3">
         <v>39400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>45300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>42700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>29300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>81100</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O89" s="3">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P89" s="3">
         <v>7700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>26300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>107600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>47800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>31700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>34600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-6600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>59300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-4200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>48600</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6566,8 +6783,11 @@
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6596,8 +6816,9 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6605,68 +6826,68 @@
         <v>3</v>
       </c>
       <c r="E91" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="F91" s="3">
         <v>-2000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="J91" s="3">
         <v>-4900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-300</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M91" s="3">
+      <c r="M91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N91" s="3">
         <v>-1400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-800</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-200</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-200</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
       <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-100</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6676,8 +6897,11 @@
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6756,8 +6980,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6836,8 +7063,11 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6845,68 +7075,68 @@
         <v>3</v>
       </c>
       <c r="E94" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="F94" s="3">
         <v>2100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>200</v>
       </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I94" s="3">
+        <v>-52800</v>
+      </c>
+      <c r="J94" s="3">
         <v>-8600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>2400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>47200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>21200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-189300</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3">
         <v>27900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-230900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-284200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>34800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-283200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-297400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>6500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>17000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-21000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>32300</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6916,8 +7146,11 @@
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6946,8 +7179,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6955,56 +7189,56 @@
         <v>3</v>
       </c>
       <c r="E96" s="3">
+        <v>23600</v>
+      </c>
+      <c r="F96" s="3">
         <v>23000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>22900</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H96" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I96" s="3">
+        <v>59900</v>
+      </c>
+      <c r="J96" s="3">
         <v>29400</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>37100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>33300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>45300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-103300</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-29700</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-23600</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-119800</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-63000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-37700</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-23300</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
         <v>0</v>
       </c>
@@ -7026,8 +7260,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7106,8 +7343,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7186,8 +7426,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7266,8 +7509,11 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7275,68 +7521,68 @@
         <v>3</v>
       </c>
       <c r="E100" s="3">
+        <v>-90100</v>
+      </c>
+      <c r="F100" s="3">
         <v>-31100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-60000</v>
       </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I100" s="3">
+        <v>22500</v>
+      </c>
+      <c r="J100" s="3">
         <v>-32600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-51600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-98200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-47200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>118500</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3">
         <v>-30500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>201100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>177900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-63500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>262400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>277300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-25600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-40600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-53300</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7346,8 +7592,11 @@
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7355,58 +7604,58 @@
         <v>3</v>
       </c>
       <c r="E101" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F101" s="3">
         <v>300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1000</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O101" s="3">
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3">
         <v>-1500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1200</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
       <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
         <v>-100</v>
-      </c>
-      <c r="S101" s="3">
-        <v>200</v>
       </c>
       <c r="T101" s="3">
         <v>200</v>
       </c>
       <c r="U101" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="V101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W101" s="3">
         <v>-100</v>
@@ -7414,8 +7663,8 @@
       <c r="X101" s="3">
         <v>-100</v>
       </c>
-      <c r="Y101" s="3" t="s">
-        <v>3</v>
+      <c r="Y101" s="3">
+        <v>-100</v>
       </c>
       <c r="Z101" s="3" t="s">
         <v>3</v>
@@ -7426,8 +7675,11 @@
       <c r="AB101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -7435,68 +7687,68 @@
         <v>0</v>
       </c>
       <c r="E102" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F102" s="3">
         <v>-4900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>9400</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
         <v>0</v>
       </c>
       <c r="I102" s="3">
+        <v>10900</v>
+      </c>
+      <c r="J102" s="3">
         <v>-1500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-4800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-8400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>4200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>11300</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O102" s="3">
+      <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3">
         <v>3500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>19100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>11100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>14700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-25600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>35600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-25800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>27600</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7504,6 +7756,9 @@
         <v>3</v>
       </c>
       <c r="AB102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PAX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PAX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="92">
   <si>
     <t>PAX</t>
   </si>
@@ -656,114 +656,115 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="E7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44834</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44742</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44651</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44561</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44469</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44377</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44286</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44196</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44104</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
@@ -773,80 +774,83 @@
       <c r="AC7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>86500</v>
+      </c>
+      <c r="E8" s="3">
         <v>82500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>79600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>157200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>78100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>75000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>63900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>111700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>63500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>78600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>73800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>91300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>57000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>55600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>55000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>46200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>39700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>119000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>30600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>31800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>83300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>35200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>88000</v>
       </c>
-      <c r="Z8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA8" s="3" t="s">
         <v>3</v>
       </c>
@@ -856,80 +860,83 @@
       <c r="AC8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>33800</v>
+      </c>
+      <c r="E9" s="3">
         <v>31900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>28700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>54800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>32500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>32400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>20300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>43300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>21700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>30400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>29300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>40800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>26000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>27400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>27600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>16400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>15200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>43100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>12000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>7200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>26000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>8700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>34200</v>
       </c>
-      <c r="Z9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
@@ -939,80 +946,83 @@
       <c r="AC9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>52700</v>
+      </c>
+      <c r="E10" s="3">
         <v>50600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>50900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>102400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>45500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>42600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>43600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>68400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>41800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>48200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>44400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>50500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>31000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>28200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>27400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>29800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>24500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>75900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>18600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>24600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>57300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>26500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>53800</v>
       </c>
-      <c r="Z10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1022,8 +1032,11 @@
       <c r="AC10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1053,8 +1066,9 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1136,8 +1150,11 @@
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1219,71 +1236,74 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E14" s="3">
         <v>4900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>5100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>19500</v>
       </c>
-      <c r="G14" s="3">
-        <v>19700</v>
-      </c>
       <c r="H14" s="3">
+        <v>8400</v>
+      </c>
+      <c r="I14" s="3">
         <v>9800</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>-7700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-2500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>12700</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3">
         <v>5100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1800</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>8900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>100</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>2400</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>2200</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1293,8 +1313,8 @@
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
@@ -1302,55 +1322,58 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E15" s="3">
         <v>9200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>9900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>10800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>7500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>6400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>6000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>6100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>5900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>5500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>4900</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P15" s="3">
+      <c r="P15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q15" s="3">
         <v>1800</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>1600</v>
-      </c>
-      <c r="R15" s="3">
-        <v>500</v>
       </c>
       <c r="S15" s="3">
         <v>500</v>
@@ -1362,20 +1385,20 @@
         <v>500</v>
       </c>
       <c r="V15" s="3">
+        <v>500</v>
+      </c>
+      <c r="W15" s="3">
         <v>400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>1300</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>500</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>1700</v>
       </c>
-      <c r="Z15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1385,8 +1408,11 @@
       <c r="AC15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1413,80 +1439,81 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>56200</v>
+      </c>
+      <c r="E17" s="3">
         <v>52800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>50600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>79700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>52200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>50000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>35500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>58000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>39100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>46000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>43200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>44400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>40900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>42100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>37100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>31700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>18300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>46900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>16800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>15100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>34700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>14600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>44000</v>
       </c>
-      <c r="Z17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1496,80 +1523,83 @@
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>30300</v>
+      </c>
+      <c r="E18" s="3">
         <v>29700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>28900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>77500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>25900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>25000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>28400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>53800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>24500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>32500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>30600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>46900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>16100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>13500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>17900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>14500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>21400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>72100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>13800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>16700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>48600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>20600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>44000</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1579,8 +1609,11 @@
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1610,80 +1643,81 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E20" s="3">
         <v>5900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>5300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1900</v>
       </c>
-      <c r="G20" s="3">
-        <v>-7800</v>
-      </c>
       <c r="H20" s="3">
+        <v>4200</v>
+      </c>
+      <c r="I20" s="3">
         <v>8800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>8000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>10500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>4200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>6400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-3200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>2700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>5200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>400</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>600</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>900</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1693,80 +1727,83 @@
       <c r="AC20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>39000</v>
+      </c>
+      <c r="E21" s="3">
         <v>33100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>33500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>86500</v>
       </c>
-      <c r="G21" s="3">
-        <v>41100</v>
-      </c>
       <c r="H21" s="3">
+        <v>29100</v>
+      </c>
+      <c r="I21" s="3">
         <v>22700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>26400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>49300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>26100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>31600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>38600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>70200</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3">
         <v>21300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>28300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>24100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>22900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>76400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>15800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>18600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>55000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>22700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>51100</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1776,28 +1813,31 @@
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E22" s="3">
         <v>4000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>3900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>3600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>3800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>3300</v>
-      </c>
-      <c r="I22" s="3">
-        <v>300</v>
       </c>
       <c r="J22" s="3">
         <v>300</v>
@@ -1811,20 +1851,20 @@
       <c r="M22" s="3">
         <v>300</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
+      <c r="N22" s="3">
+        <v>300</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3">
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="3">
         <v>700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>600</v>
-      </c>
-      <c r="R22" s="3">
-        <v>300</v>
       </c>
       <c r="S22" s="3">
         <v>300</v>
@@ -1836,20 +1876,20 @@
         <v>300</v>
       </c>
       <c r="V22" s="3">
+        <v>300</v>
+      </c>
+      <c r="W22" s="3">
         <v>200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>800</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1859,80 +1899,83 @@
       <c r="AC22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>24600</v>
+      </c>
+      <c r="E23" s="3">
         <v>15000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>14600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>52600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>10200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>20100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>50700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>18300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>28300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>20700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>49000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>15400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>15600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>22500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>15100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>20700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>72200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>13600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>16500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>48500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>20300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>44100</v>
       </c>
-      <c r="Z23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1942,80 +1985,83 @@
       <c r="AC23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>400</v>
+      </c>
+      <c r="E24" s="3">
         <v>800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-2000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-2800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>8300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>4200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-7700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>3100</v>
-      </c>
-      <c r="N24" s="3">
-        <v>2200</v>
       </c>
       <c r="O24" s="3">
         <v>2200</v>
       </c>
       <c r="P24" s="3">
+        <v>2200</v>
+      </c>
+      <c r="Q24" s="3">
         <v>-300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>4200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-1200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>3000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>2700</v>
       </c>
-      <c r="Z24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA24" s="3" t="s">
         <v>3</v>
       </c>
@@ -2025,8 +2071,11 @@
       <c r="AC24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2108,80 +2157,83 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>24200</v>
+      </c>
+      <c r="E26" s="3">
         <v>14100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>16600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>55400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>15900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>48400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>18800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>36000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>17600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>46700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>13200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>15900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>18300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>13200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>21500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>73400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>13100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>16300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>45500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>19600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>41400</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2191,80 +2243,83 @@
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>22600</v>
+      </c>
+      <c r="E27" s="3">
         <v>12900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>15700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>55300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>15400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>47000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>18500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>35700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>17200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>46600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>12200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>15900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>18300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>13200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>21500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>73400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>14300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>15600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>46600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>18700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>39800</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2274,8 +2329,11 @@
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2357,8 +2415,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2440,8 +2501,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2523,8 +2587,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2606,80 +2673,83 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-5900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-5300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1900</v>
       </c>
-      <c r="G32" s="3">
-        <v>7800</v>
-      </c>
       <c r="H32" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="I32" s="3">
         <v>-8800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-8000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-10500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-4200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-6400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>3200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-5200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-400</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>-600</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-900</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2689,80 +2759,83 @@
       <c r="AC32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>22600</v>
+      </c>
+      <c r="E33" s="3">
         <v>12900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>15700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>55300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>15400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>47000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>18500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>35700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>17200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>46600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>12200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>15900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>18300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>13200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>21500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>73400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>14300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>15600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>46600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>18700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>39800</v>
       </c>
-      <c r="Z33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2772,8 +2845,11 @@
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2855,80 +2931,83 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>22600</v>
+      </c>
+      <c r="E35" s="3">
         <v>12900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>15700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>55300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>15400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>47000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>18500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>35700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>17200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>46600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>12200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>15900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>18300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>13200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>21500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>73400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>14300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>15600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>46600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>18700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>39800</v>
       </c>
-      <c r="Z35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2938,85 +3017,88 @@
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="E38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44834</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44742</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44651</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44561</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44469</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44377</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44286</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44196</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44104</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3026,8 +3108,11 @@
       <c r="AC38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3057,8 +3142,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3088,74 +3174,75 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>30300</v>
+      </c>
+      <c r="E41" s="3">
         <v>28500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>36100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>33400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>38300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>28900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>17300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>16100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>17500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>22400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>30800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>21400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>24400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>13400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>12900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>15300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>44300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>25200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>28700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>14100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>39700</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3171,74 +3258,77 @@
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E42" s="3">
         <v>26700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>14600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>5000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>9700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>17800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>197600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>17200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>21600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>24900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>10500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>291000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>317000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>328400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>136000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>151900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>250800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>286300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>300400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>9900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>11600</v>
       </c>
-      <c r="X42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3254,74 +3344,77 @@
       <c r="AC42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>101400</v>
+      </c>
+      <c r="E43" s="3">
         <v>96500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>172100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>227100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>131900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>126300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>127100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>134600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>118900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>115700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>147600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>137900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>95900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>95600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>105400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>103500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>122300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>113700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>24400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>26000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>10000</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3337,8 +3430,11 @@
       <c r="AC43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3372,8 +3468,8 @@
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N44" s="3">
-        <v>0</v>
+      <c r="N44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O44" s="3">
         <v>0</v>
@@ -3420,74 +3516,77 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>82700</v>
+      </c>
+      <c r="E45" s="3">
         <v>152100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>166100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>100100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>249800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>152700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>104800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>227700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>208000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>210600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>269100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>29300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>51600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>55500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>83900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>81700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>4000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1800</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3503,74 +3602,77 @@
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>245300</v>
+      </c>
+      <c r="E46" s="3">
         <v>312200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>397200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>372700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>437900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>333800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>446800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>401600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>372400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>377800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>462300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>479600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>488900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>492900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>338200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>352300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>421400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>428200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>355500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>53700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>63100</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3586,74 +3688,77 @@
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>46000</v>
+      </c>
+      <c r="E47" s="3">
         <v>40200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>59900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>50000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>48400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>49300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>52600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>58600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>54100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>55200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>62700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>50400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>58600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>44100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>282900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>30000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>30600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>31100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>30400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>24500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>36500</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3669,74 +3774,77 @@
       <c r="AC47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>40700</v>
+      </c>
+      <c r="E48" s="3">
         <v>38500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>34900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>32600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>27500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>27700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>28800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>28200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>23800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>25400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>25200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>24600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>24000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>18300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>15800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>13400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>4000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>4100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3900</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3752,74 +3860,77 @@
       <c r="AC48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>829400</v>
+      </c>
+      <c r="E49" s="3">
         <v>795100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>777100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>700900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>750400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>712600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>473500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>487000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>438400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>451000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>422600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>411500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>359500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>339800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>366300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>358900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>18300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>19300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>21400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>22400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>23700</v>
       </c>
-      <c r="X49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3835,8 +3946,11 @@
       <c r="AC49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3918,8 +4032,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4001,74 +4118,77 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>40600</v>
+      </c>
+      <c r="E52" s="3">
         <v>26000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>27700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>14100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>45500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>25900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>7100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>9000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>9900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>10700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>10000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5700</v>
-      </c>
-      <c r="P52" s="3">
-        <v>5500</v>
       </c>
       <c r="Q52" s="3">
         <v>5500</v>
       </c>
       <c r="R52" s="3">
+        <v>5500</v>
+      </c>
+      <c r="S52" s="3">
         <v>6700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2800</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4084,8 +4204,11 @@
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4167,74 +4290,77 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1325500</v>
+      </c>
+      <c r="E54" s="3">
         <v>1318000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1334000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1206100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1345500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1182000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1044400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1011600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>929600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>949400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>999800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>976200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>936700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>900700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1008700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>761300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>478500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>486400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>413500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>107200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>130000</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4250,8 +4376,11 @@
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4281,8 +4410,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4312,44 +4442,45 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>48900</v>
+      </c>
+      <c r="E57" s="3">
         <v>34600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>66300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>41800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>26200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>12200</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="J57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K57" s="3">
         <v>4800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5100</v>
       </c>
-      <c r="N57" s="3">
-        <v>0</v>
-      </c>
       <c r="O57" s="3">
         <v>0</v>
       </c>
@@ -4395,74 +4526,77 @@
       <c r="AC57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>46000</v>
+      </c>
+      <c r="E58" s="3">
         <v>90800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>45900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>82200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>19500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>31700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>10000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3000</v>
-      </c>
-      <c r="K58" s="3">
-        <v>2900</v>
       </c>
       <c r="L58" s="3">
         <v>2900</v>
       </c>
       <c r="M58" s="3">
+        <v>2900</v>
+      </c>
+      <c r="N58" s="3">
         <v>2600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2200</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P58" s="3">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="3">
         <v>1200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>700</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4478,74 +4612,77 @@
       <c r="AC58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>210800</v>
+      </c>
+      <c r="E59" s="3">
         <v>235900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>245200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>201400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>390900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>299600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>363300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>349500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>279900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>248400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>336500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>335800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>347600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>312600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>164600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>155300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>84700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>51400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>38600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>43300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>33900</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4561,74 +4698,77 @@
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>356600</v>
+      </c>
+      <c r="E60" s="3">
         <v>401900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>410800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>397400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>481700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>378100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>394400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>397500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>316000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>281200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>365400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>338000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>347600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>313900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>166200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>156200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>85600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>52400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>39500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>44000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>34600</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4644,74 +4784,77 @@
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>125300</v>
+      </c>
+      <c r="E61" s="3">
         <v>95900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>169000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>168200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>163600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>162700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>120300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>12800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>12700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>14100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>14200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>13900</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
         <v>8800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>7300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>6900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>900</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -4727,74 +4870,77 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>188300</v>
+      </c>
+      <c r="E62" s="3">
         <v>180800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>148200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>147800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>214100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>153700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>41100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>79900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>127500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>146900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>125500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>110900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>73500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>44500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>261900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>33900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3900</v>
-      </c>
-      <c r="T62" s="3">
-        <v>2900</v>
       </c>
       <c r="U62" s="3">
         <v>2900</v>
       </c>
       <c r="V62" s="3">
+        <v>2900</v>
+      </c>
+      <c r="W62" s="3">
         <v>3300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>4400</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4810,8 +4956,11 @@
       <c r="AC62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4893,8 +5042,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4976,8 +5128,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5059,74 +5214,77 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>722400</v>
+      </c>
+      <c r="E66" s="3">
         <v>729200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>777800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>715200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>861900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>697400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>555800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>490200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>456300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>442200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>505400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>423500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>422300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>367200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>435300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>197000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>90300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>56300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>43200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>49900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>40100</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5142,8 +5300,11 @@
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5173,8 +5334,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5256,8 +5418,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5339,8 +5504,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5422,8 +5590,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5505,8 +5676,11 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -5525,54 +5699,54 @@
       <c r="H72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I72" s="3">
+      <c r="I72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J72" s="3">
         <v>8400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>50800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>33300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>51900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>49500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>79100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>56200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>70000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>83700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>88700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>94500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>135900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>76300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>62000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>96200</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5588,8 +5762,11 @@
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5671,8 +5848,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5754,8 +5934,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5837,74 +6020,77 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>586400</v>
+      </c>
+      <c r="E76" s="3">
         <v>575100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>545500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>481100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>475300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>514800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>505200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>542500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>514200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>551100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>539200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>552800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>514400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>533500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>573400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>564300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>388200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>430100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>370300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>57300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>89900</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5920,8 +6106,11 @@
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6003,85 +6192,88 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="E80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44834</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44742</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44651</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44561</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44469</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44377</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44286</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44196</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44104</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
@@ -6091,80 +6283,83 @@
       <c r="AC80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>22600</v>
+      </c>
+      <c r="E81" s="3">
         <v>12900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>15700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>55300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>15400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>47000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>18500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>35700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>17200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>46600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>12200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>15900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>18300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>13200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>21500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>73400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>14300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>15600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>46600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>18700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>39800</v>
       </c>
-      <c r="Z81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
@@ -6174,8 +6369,11 @@
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6205,8 +6403,9 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6214,71 +6413,71 @@
         <v>1300</v>
       </c>
       <c r="E83" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F83" s="3">
         <v>1200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1200</v>
-      </c>
-      <c r="I83" s="3">
-        <v>1100</v>
       </c>
       <c r="J83" s="3">
         <v>1100</v>
       </c>
       <c r="K83" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="L83" s="3">
         <v>1000</v>
       </c>
       <c r="M83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N83" s="3">
         <v>800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>21200</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P83" s="3">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3">
         <v>5100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>5200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>8800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>3900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>2000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>5800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>2100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>6200</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6288,8 +6487,11 @@
       <c r="AC83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6371,8 +6573,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6454,8 +6659,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6537,8 +6745,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6620,8 +6831,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6703,80 +6917,83 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>65900</v>
+      </c>
+      <c r="E89" s="3">
         <v>76900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>100100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>25900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>68400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>9700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>41900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>39400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>45300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>42700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>29300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>81100</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P89" s="3">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3">
         <v>7700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>26300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>107600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>47800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>31700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>34600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-6600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>59300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-4200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>48600</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6786,8 +7003,11 @@
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6817,80 +7037,81 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-300</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N91" s="3">
+      <c r="N91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O91" s="3">
         <v>-1400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-800</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
         <v>-200</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
         <v>-200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-200</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
       <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-100</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6900,8 +7121,11 @@
       <c r="AC91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6983,8 +7207,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7066,80 +7293,83 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>62300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-32000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-9400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>2100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>75800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-52800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-8600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>2400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>47200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>21200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-189300</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P94" s="3">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3">
         <v>27900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-230900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-284200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>34800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-283200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-297400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>6500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>17000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-21000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>32300</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
@@ -7149,8 +7379,11 @@
       <c r="AC94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7180,68 +7413,69 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>23900</v>
+      </c>
+      <c r="E96" s="3">
         <v>23700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>23600</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>23000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>22900</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>26600</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>59900</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>29400</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>37100</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>33300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>45300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-103300</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-29700</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-23600</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-119800</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-63000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-37700</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-23300</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
         <v>0</v>
       </c>
@@ -7263,8 +7497,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7346,8 +7583,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7429,8 +7669,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7512,80 +7755,83 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-126100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-53300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-90100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-31100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-60000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-83100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>22500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-32600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-51600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-98200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-47200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>118500</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-30500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>201100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>177900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-63500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>262400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>277300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-25600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-40600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-53300</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7595,70 +7841,73 @@
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>800</v>
+      </c>
+      <c r="E101" s="3">
         <v>-400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1000</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P101" s="3">
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1200</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
       <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
         <v>-100</v>
-      </c>
-      <c r="T101" s="3">
-        <v>200</v>
       </c>
       <c r="U101" s="3">
         <v>200</v>
       </c>
       <c r="V101" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="W101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="X101" s="3">
         <v>-100</v>
@@ -7666,8 +7915,8 @@
       <c r="Y101" s="3">
         <v>-100</v>
       </c>
-      <c r="Z101" s="3" t="s">
-        <v>3</v>
+      <c r="Z101" s="3">
+        <v>-100</v>
       </c>
       <c r="AA101" s="3" t="s">
         <v>3</v>
@@ -7678,80 +7927,83 @@
       <c r="AC101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-7500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-4900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>9400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>10900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-4800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-8400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>4200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>11300</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P102" s="3">
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3">
         <v>3500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>19100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>11100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>14700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-25600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>35600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-25800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>27600</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7759,6 +8011,9 @@
         <v>3</v>
       </c>
       <c r="AC102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PAX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PAX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="92">
   <si>
     <t>PAX</t>
   </si>
@@ -656,118 +656,118 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
@@ -777,83 +777,86 @@
       <c r="AD7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>133200</v>
+      </c>
+      <c r="E8" s="3">
         <v>86500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>82500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>79600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>157200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>78100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>75000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>63900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>111700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>63500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>78600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>73800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>91300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>57000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>55600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>55000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>46200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>39700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>119000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>30600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>31800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>83300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>35200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>88000</v>
       </c>
-      <c r="AA8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB8" s="3" t="s">
         <v>3</v>
       </c>
@@ -863,83 +866,86 @@
       <c r="AD8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>54500</v>
+      </c>
+      <c r="E9" s="3">
         <v>33800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>31900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>28700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>54800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>32500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>32400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>20300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>43300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>21700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>30400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>29300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>40800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>26000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>27400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>27600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>16400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>15200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>43100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>12000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>7200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>26000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>8700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>34200</v>
       </c>
-      <c r="AA9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB9" s="3" t="s">
         <v>3</v>
       </c>
@@ -949,83 +955,86 @@
       <c r="AD9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>78600</v>
+      </c>
+      <c r="E10" s="3">
         <v>52700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>50600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>50900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>102400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>45500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>42600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>43600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>68400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>41800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>48200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>44400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>50500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>31000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>28200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>27400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>29800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>24500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>75900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>18600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>24600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>57300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>26500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>53800</v>
       </c>
-      <c r="AA10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1035,8 +1044,11 @@
       <c r="AD10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1067,8 +1079,9 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1153,8 +1166,11 @@
       <c r="AD12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1239,74 +1255,77 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>28700</v>
+      </c>
+      <c r="E14" s="3">
         <v>2800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>4900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>5100</v>
       </c>
-      <c r="G14" s="3">
-        <v>19500</v>
-      </c>
       <c r="H14" s="3">
-        <v>8400</v>
+        <v>38000</v>
       </c>
       <c r="I14" s="3">
+        <v>12400</v>
+      </c>
+      <c r="J14" s="3">
         <v>9800</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>-7700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-2500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>12700</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3">
         <v>5100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>8900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>100</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>2400</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>2200</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1316,8 +1335,8 @@
       <c r="AA14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC14" s="3">
         <v>0</v>
@@ -1325,58 +1344,61 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E15" s="3">
         <v>10500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>9200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>9900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>10800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>7500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>6400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>6000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>6100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>5900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>5500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>4900</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="Q15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R15" s="3">
         <v>1800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>1600</v>
-      </c>
-      <c r="S15" s="3">
-        <v>500</v>
       </c>
       <c r="T15" s="3">
         <v>500</v>
@@ -1388,20 +1410,20 @@
         <v>500</v>
       </c>
       <c r="W15" s="3">
+        <v>500</v>
+      </c>
+      <c r="X15" s="3">
         <v>400</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>1300</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>1700</v>
       </c>
-      <c r="AA15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1411,8 +1433,11 @@
       <c r="AD15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1440,83 +1465,84 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>79900</v>
+      </c>
+      <c r="E17" s="3">
         <v>56200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>52800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>50600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>79700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>52200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>50000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>35500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>58000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>39100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>46000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>43200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>44400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>40900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>42100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>37100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>31700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>18300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>46900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>16800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>15100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>34700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>14600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>44000</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1526,83 +1552,86 @@
       <c r="AD17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>53300</v>
+      </c>
+      <c r="E18" s="3">
         <v>30300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>29700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>28900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>77500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>25900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>25000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>28400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>53800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>24500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>32500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>30600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>46900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>16100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>13500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>17900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>14500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>21400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>72100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>13800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>16700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>48600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>20600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>44000</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1612,8 +1641,11 @@
       <c r="AD18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1644,83 +1676,84 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-15600</v>
+      </c>
+      <c r="E20" s="3">
         <v>1800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>5900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>5300</v>
       </c>
-      <c r="G20" s="3">
-        <v>1900</v>
-      </c>
       <c r="H20" s="3">
+        <v>-16200</v>
+      </c>
+      <c r="I20" s="3">
+        <v>300</v>
+      </c>
+      <c r="J20" s="3">
+        <v>8800</v>
+      </c>
+      <c r="K20" s="3">
+        <v>8000</v>
+      </c>
+      <c r="L20" s="3">
+        <v>10500</v>
+      </c>
+      <c r="M20" s="3">
         <v>4200</v>
       </c>
-      <c r="I20" s="3">
-        <v>8800</v>
-      </c>
-      <c r="J20" s="3">
-        <v>8000</v>
-      </c>
-      <c r="K20" s="3">
-        <v>10500</v>
-      </c>
-      <c r="L20" s="3">
-        <v>4200</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>6400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-3200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>2100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>5200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>400</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>600</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>900</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1730,83 +1763,86 @@
       <c r="AD20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>78900</v>
+      </c>
+      <c r="E21" s="3">
         <v>39000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>33100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>33500</v>
       </c>
-      <c r="G21" s="3">
-        <v>86500</v>
-      </c>
       <c r="H21" s="3">
-        <v>29100</v>
+        <v>104500</v>
       </c>
       <c r="I21" s="3">
+        <v>33000</v>
+      </c>
+      <c r="J21" s="3">
         <v>22700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>26400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>49300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>26100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>31600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>38600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>70200</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3">
         <v>21300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>28300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>24100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>22900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>76400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>15800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>18600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>55000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>22700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>51100</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1816,31 +1852,34 @@
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E22" s="3">
         <v>5100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>4000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>3900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>3600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>3800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>3300</v>
-      </c>
-      <c r="J22" s="3">
-        <v>300</v>
       </c>
       <c r="K22" s="3">
         <v>300</v>
@@ -1854,20 +1893,20 @@
       <c r="N22" s="3">
         <v>300</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
+      <c r="O22" s="3">
+        <v>300</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R22" s="3">
         <v>700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>600</v>
-      </c>
-      <c r="S22" s="3">
-        <v>300</v>
       </c>
       <c r="T22" s="3">
         <v>300</v>
@@ -1879,20 +1918,20 @@
         <v>300</v>
       </c>
       <c r="W22" s="3">
+        <v>300</v>
+      </c>
+      <c r="X22" s="3">
         <v>200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>800</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1902,83 +1941,86 @@
       <c r="AD22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>38100</v>
+      </c>
+      <c r="E23" s="3">
         <v>24600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>15000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>14600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>52600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>10200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>20100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>50700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>18300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>28300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>20700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>49000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>15400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>15600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>22500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>15100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>20700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>72200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>13600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>16500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>48500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>20300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>44100</v>
       </c>
-      <c r="AA23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1988,83 +2030,86 @@
       <c r="AD23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E24" s="3">
         <v>400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-2000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-2800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>8300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-7700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>3100</v>
-      </c>
-      <c r="O24" s="3">
-        <v>2200</v>
       </c>
       <c r="P24" s="3">
         <v>2200</v>
       </c>
       <c r="Q24" s="3">
+        <v>2200</v>
+      </c>
+      <c r="R24" s="3">
         <v>-300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>4200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-1200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>3000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>2700</v>
       </c>
-      <c r="AA24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB24" s="3" t="s">
         <v>3</v>
       </c>
@@ -2074,8 +2119,11 @@
       <c r="AD24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2160,83 +2208,86 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>35700</v>
+      </c>
+      <c r="E26" s="3">
         <v>24200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>14100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>16600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>55400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>15900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>48400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>18800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>36000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>17600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>46700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>13200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>15900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>18300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>13200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>21500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>73400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>13100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>16300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>45500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>19600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>41400</v>
       </c>
-      <c r="AA26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2246,83 +2297,86 @@
       <c r="AD26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>34600</v>
+      </c>
+      <c r="E27" s="3">
         <v>22600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>12900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>15700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>55300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>15400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>47000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>18500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>35700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>17200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>46600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>12200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>15900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>18300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>13200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>21500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>73400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>14300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>15600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>46600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>18700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>39800</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2332,8 +2386,11 @@
       <c r="AD27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2418,8 +2475,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2504,8 +2564,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2590,8 +2653,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2676,83 +2742,86 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-5900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-5300</v>
       </c>
-      <c r="G32" s="3">
-        <v>-1900</v>
-      </c>
       <c r="H32" s="3">
+        <v>16200</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="L32" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="M32" s="3">
         <v>-4200</v>
       </c>
-      <c r="I32" s="3">
-        <v>-8800</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-8000</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-10500</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-6400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>3200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-2100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-5200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-400</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-600</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-900</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2762,83 +2831,86 @@
       <c r="AD32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>34600</v>
+      </c>
+      <c r="E33" s="3">
         <v>22600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>12900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>15700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>55300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>15400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>47000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>18500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>35700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>17200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>46600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>12200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>15900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>18300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>13200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>21500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>73400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>14300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>15600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>46600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>18700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>39800</v>
       </c>
-      <c r="AA33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2848,8 +2920,11 @@
       <c r="AD33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2934,83 +3009,86 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>34600</v>
+      </c>
+      <c r="E35" s="3">
         <v>22600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>12900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>15700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>55300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>15400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>47000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>18500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>35700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>17200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>46600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>12200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>15900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>18300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>13200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>21500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>73400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>14300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>15600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>46600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>18700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>39800</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
@@ -3020,88 +3098,91 @@
       <c r="AD35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3111,8 +3192,11 @@
       <c r="AD38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3143,8 +3227,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3175,77 +3260,78 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>53600</v>
+      </c>
+      <c r="E41" s="3">
         <v>30300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>28500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>36100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>33400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>38300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>28900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>17300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>16100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>17500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>22400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>30800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>21400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>24400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>13400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>12900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>15300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>44300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>25200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>28700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>14100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>39700</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3261,77 +3347,80 @@
       <c r="AD41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>35100</v>
+      </c>
+      <c r="E42" s="3">
         <v>22000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>26700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>14600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>5000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>9700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>17800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>197600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>17200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>21600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>24900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>10500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>291000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>317000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>328400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>136000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>151900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>250800</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>286300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>300400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>9900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>11600</v>
       </c>
-      <c r="Y42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3347,77 +3436,80 @@
       <c r="AD42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>138700</v>
+      </c>
+      <c r="E43" s="3">
         <v>101400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>96500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>172100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>227100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>131900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>126300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>127100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>134600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>118900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>115700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>147600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>137900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>95900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>95600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>105400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>103500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>122300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>113700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>24400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>26000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>10000</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3433,8 +3525,11 @@
       <c r="AD43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3471,8 +3566,8 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -3519,77 +3614,80 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>174000</v>
+      </c>
+      <c r="E45" s="3">
         <v>82700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>152100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>166100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>100100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>249800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>152700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>104800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>227700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>208000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>210600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>269100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>29300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>51600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>55500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>83900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>81700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>4000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>3700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1800</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3605,77 +3703,80 @@
       <c r="AD45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>405300</v>
+      </c>
+      <c r="E46" s="3">
         <v>245300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>312200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>397200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>372700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>437900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>333800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>446800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>401600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>372400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>377800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>462300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>479600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>488900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>492900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>338200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>352300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>421400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>428200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>355500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>53700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>63100</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3691,77 +3792,80 @@
       <c r="AD46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>44600</v>
+      </c>
+      <c r="E47" s="3">
         <v>46000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>40200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>59900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>50000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>48400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>49300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>52600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>58600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>54100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>55200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>62700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>50400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>58600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>44100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>282900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>30000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>30600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>31100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>30400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>24500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>36500</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3777,77 +3881,80 @@
       <c r="AD47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>42400</v>
+      </c>
+      <c r="E48" s="3">
         <v>40700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>38500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>34900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>32600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>27500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>27700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>28800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>28200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>23800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>25400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>25200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>24600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>24000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>18300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>15800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>13400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>4000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>4100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3900</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3863,77 +3970,80 @@
       <c r="AD48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>824200</v>
+      </c>
+      <c r="E49" s="3">
         <v>829400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>795100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>777100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>700900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>750400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>712600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>473500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>487000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>438400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>451000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>422600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>411500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>359500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>339800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>366300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>358900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>18300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>19300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>21400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>22400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>23700</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3949,8 +4059,11 @@
       <c r="AD49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4035,8 +4148,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4121,77 +4237,80 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>56000</v>
+      </c>
+      <c r="E52" s="3">
         <v>40600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>26000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>27700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>14100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>45500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>25900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>7100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>9000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>9900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>10700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>10000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5700</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>5500</v>
       </c>
       <c r="R52" s="3">
         <v>5500</v>
       </c>
       <c r="S52" s="3">
+        <v>5500</v>
+      </c>
+      <c r="T52" s="3">
         <v>6700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2800</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4207,8 +4326,11 @@
       <c r="AD52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4293,77 +4415,80 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1495100</v>
+      </c>
+      <c r="E54" s="3">
         <v>1325500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1318000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1334000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1206100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1345500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1182000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1044400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1011600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>929600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>949400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>999800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>976200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>936700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>900700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1008700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>761300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>478500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>486400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>413500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>107200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>130000</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4379,8 +4504,11 @@
       <c r="AD54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4411,8 +4539,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4443,47 +4572,48 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>58800</v>
+      </c>
+      <c r="E57" s="3">
         <v>48900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>34600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>66300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>41800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>26200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>12200</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L57" s="3">
         <v>4800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5100</v>
       </c>
-      <c r="O57" s="3">
-        <v>0</v>
-      </c>
       <c r="P57" s="3">
         <v>0</v>
       </c>
@@ -4529,77 +4659,80 @@
       <c r="AD57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E58" s="3">
         <v>46000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>90800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>45900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>82200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>19500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>31700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>10000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3000</v>
-      </c>
-      <c r="L58" s="3">
-        <v>2900</v>
       </c>
       <c r="M58" s="3">
         <v>2900</v>
       </c>
       <c r="N58" s="3">
+        <v>2900</v>
+      </c>
+      <c r="O58" s="3">
         <v>2600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2200</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q58" s="3">
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R58" s="3">
         <v>1200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>700</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4615,77 +4748,80 @@
       <c r="AD58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>270700</v>
+      </c>
+      <c r="E59" s="3">
         <v>210800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>235900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>245200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>201400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>390900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>299600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>363300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>349500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>279900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>248400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>336500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>335800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>347600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>312600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>164600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>155300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>84700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>51400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>38600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>43300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>33900</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4701,77 +4837,80 @@
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>415000</v>
+      </c>
+      <c r="E60" s="3">
         <v>356600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>401900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>410800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>397400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>481700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>378100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>394400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>397500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>316000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>281200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>365400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>338000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>347600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>313900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>166200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>156200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>85600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>52400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>39500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>44000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>34600</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4787,77 +4926,80 @@
       <c r="AD60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>194400</v>
+      </c>
+      <c r="E61" s="3">
         <v>125300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>95900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>169000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>168200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>163600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>162700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>120300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>12800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>12700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>14100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>14200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>13900</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
         <v>8800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>7300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>6900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>900</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
         <v>0</v>
       </c>
@@ -4873,77 +5015,80 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>200000</v>
+      </c>
+      <c r="E62" s="3">
         <v>188300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>180800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>148200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>147800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>214100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>153700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>41100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>79900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>127500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>146900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>125500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>110900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>73500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>44500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>261900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>33900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3900</v>
-      </c>
-      <c r="U62" s="3">
-        <v>2900</v>
       </c>
       <c r="V62" s="3">
         <v>2900</v>
       </c>
       <c r="W62" s="3">
+        <v>2900</v>
+      </c>
+      <c r="X62" s="3">
         <v>3300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>4400</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4959,8 +5104,11 @@
       <c r="AD62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5045,8 +5193,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5131,8 +5282,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5217,77 +5371,80 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>861700</v>
+      </c>
+      <c r="E66" s="3">
         <v>722400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>729200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>777800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>715200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>861900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>697400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>555800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>490200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>456300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>442200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>505400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>423500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>422300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>367200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>435300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>197000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>90300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>56300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>43200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>49900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>40100</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5303,8 +5460,11 @@
       <c r="AD66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5335,8 +5495,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5421,8 +5582,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5507,8 +5671,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5593,8 +5760,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5679,8 +5849,11 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -5702,54 +5875,54 @@
       <c r="I72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J72" s="3">
+      <c r="J72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K72" s="3">
         <v>8400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>50800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>33300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>51900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>49500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>79100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>56200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>70000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>83700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>88700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>94500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>135900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>76300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>62000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>96200</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5765,8 +5938,11 @@
       <c r="AD72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5851,8 +6027,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5937,8 +6116,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6023,77 +6205,80 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>611800</v>
+      </c>
+      <c r="E76" s="3">
         <v>586400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>575100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>545500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>481100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>475300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>514800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>505200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>542500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>514200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>551100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>539200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>552800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>514400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>533500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>573400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>564300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>388200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>430100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>370300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>57300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>89900</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6109,8 +6294,11 @@
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6195,88 +6383,91 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
@@ -6286,83 +6477,86 @@
       <c r="AD80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>34600</v>
+      </c>
+      <c r="E81" s="3">
         <v>22600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>12900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>15700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>55300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>15400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>47000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>18500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>35700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>17200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>46600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>12200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>15900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>18300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>13200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>21500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>73400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>14300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>15600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>46600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>18700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>39800</v>
       </c>
-      <c r="AA81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
@@ -6372,8 +6566,11 @@
       <c r="AD81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6404,8 +6601,9 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6416,71 +6614,71 @@
         <v>1300</v>
       </c>
       <c r="F83" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G83" s="3">
         <v>1200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1200</v>
-      </c>
-      <c r="J83" s="3">
-        <v>1100</v>
       </c>
       <c r="K83" s="3">
         <v>1100</v>
       </c>
       <c r="L83" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="M83" s="3">
         <v>1000</v>
       </c>
       <c r="N83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="O83" s="3">
         <v>800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>21200</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3">
         <v>5100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>5200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>8800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>3900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>2000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>5800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>2100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>6200</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6490,8 +6688,11 @@
       <c r="AD83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6576,8 +6777,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6662,8 +6866,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6748,8 +6955,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6834,8 +7044,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6920,83 +7133,86 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>39800</v>
+      </c>
+      <c r="E89" s="3">
         <v>65900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>76900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>100100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>25900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>68400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>9700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>41900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>39400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>45300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>42700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>29300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>81100</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q89" s="3">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3">
         <v>7700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>26300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>107600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>47800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>31700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>34600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-6600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>59300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-4200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>48600</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
@@ -7006,8 +7222,11 @@
       <c r="AD89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7038,83 +7257,84 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-300</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O91" s="3">
+      <c r="O91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P91" s="3">
         <v>-1400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-800</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-200</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
         <v>-200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-200</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
-      </c>
       <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-100</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
@@ -7124,8 +7344,11 @@
       <c r="AD91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7210,8 +7433,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7296,83 +7522,86 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-18600</v>
+      </c>
+      <c r="E94" s="3">
         <v>62300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-32000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-9400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>2100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>75800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-52800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-8600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>2400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>47200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>21200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-189300</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q94" s="3">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3">
         <v>27900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-230900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-284200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>34800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-283200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-297400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>6500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>17000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-21000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>32300</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
@@ -7382,8 +7611,11 @@
       <c r="AD94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7414,8 +7646,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7423,62 +7656,62 @@
         <v>23900</v>
       </c>
       <c r="E96" s="3">
+        <v>23900</v>
+      </c>
+      <c r="F96" s="3">
         <v>23700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>23600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>23000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>22900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>26600</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>59900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>29400</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>37100</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>33300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>45300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-103300</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-29700</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-23600</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-119800</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-63000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-37700</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-23300</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
         <v>0</v>
       </c>
@@ -7500,8 +7733,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7586,8 +7822,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7672,8 +7911,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7758,83 +8000,86 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-126100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-53300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-90100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-31100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-60000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-83100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>22500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-32600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-51600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-98200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-47200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>118500</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3">
         <v>-30500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>201100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>177900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-63500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>262400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>277300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-25600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-40600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-53300</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7844,73 +8089,76 @@
       <c r="AD100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E101" s="3">
         <v>800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1000</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q101" s="3">
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R101" s="3">
         <v>-1500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>1200</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
       <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
         <v>-100</v>
-      </c>
-      <c r="U101" s="3">
-        <v>200</v>
       </c>
       <c r="V101" s="3">
         <v>200</v>
       </c>
       <c r="W101" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="X101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Y101" s="3">
         <v>-100</v>
@@ -7918,8 +8166,8 @@
       <c r="Z101" s="3">
         <v>-100</v>
       </c>
-      <c r="AA101" s="3" t="s">
-        <v>3</v>
+      <c r="AA101" s="3">
+        <v>-100</v>
       </c>
       <c r="AB101" s="3" t="s">
         <v>3</v>
@@ -7930,83 +8178,86 @@
       <c r="AD101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>23300</v>
+      </c>
+      <c r="E102" s="3">
         <v>1800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-7500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-4900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>9400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>10900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-4800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-8400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>4200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>11300</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q102" s="3">
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3">
         <v>3500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-2400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>19100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>11100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>14700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-25600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>35600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-25800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>27600</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
@@ -8014,6 +8265,9 @@
         <v>3</v>
       </c>
       <c r="AD102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
